--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
@@ -1221,7 +1221,7 @@
         <v>13</v>
       </c>
       <c r="Q2" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>8</v>
@@ -1242,16 +1242,16 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AA2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AB2" t="n">
         <v>5</v>
@@ -1260,7 +1260,7 @@
         <v>21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AE2" t="n">
         <v>1</v>
@@ -1725,7 +1725,7 @@
         <v>6</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>6</v>
@@ -1746,25 +1746,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AC4" t="n">
         <v>21</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.42</v>
+        <v>1.74</v>
       </c>
       <c r="AE4" t="n">
         <v>1</v>
@@ -2192,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -2267,7 +2267,7 @@
         <v>1.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
         <v>5</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AS7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
         <v>1</v>
@@ -2519,16 +2519,16 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
         <v>7</v>
@@ -2537,7 +2537,7 @@
         <v>16</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="BF7" t="n">
         <v>0</v>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>1</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL8" t="n">
         <v>3</v>
@@ -2790,7 +2790,7 @@
         <v>0.77</v>
       </c>
       <c r="BF8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG8" t="n">
         <v>1</v>
@@ -2967,10 +2967,10 @@
         <v>13</v>
       </c>
       <c r="Q9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -3252,10 +3252,10 @@
         <v>6</v>
       </c>
       <c r="AR10" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT10" t="n">
         <v>1</v>
@@ -3273,7 +3273,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
         <v>12</v>
       </c>
       <c r="AR12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="AS12" t="n">
         <v>3</v>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
@@ -137,9 +137,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Finland_Ve" displayName="AveragesTable_Finland_Ve" ref="A1:CZ13" headerRowCount="1">
-  <autoFilter ref="A1:CZ13"/>
-  <tableColumns count="104">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Finland_Ve" displayName="AveragesTable_Finland_Ve" ref="A1:EA13" headerRowCount="1">
+  <autoFilter ref="A1:EA13"/>
+  <tableColumns count="131">
     <tableColumn id="1" name="team_name"/>
     <tableColumn id="2" name="total_games"/>
     <tableColumn id="3" name="home_games"/>
@@ -235,15 +235,42 @@
     <tableColumn id="93" name="avg_odds_ft_over15"/>
     <tableColumn id="94" name="avg_odds_ft_over25"/>
     <tableColumn id="95" name="avg_odds_ft_over35"/>
-    <tableColumn id="96" name="avg_pinnacle_1st_half_over15_odd"/>
-    <tableColumn id="97" name="avg_pinnacle_1st_half_under15_odd"/>
-    <tableColumn id="98" name="avg_pinnacle_corners_over_85_odd"/>
-    <tableColumn id="99" name="avg_pinnacle_corners_over_95_odd"/>
-    <tableColumn id="100" name="avg_pinnacle_corners_under_85_odd"/>
-    <tableColumn id="101" name="avg_pinnacle_corners_under_95_odd"/>
-    <tableColumn id="102" name="avg_pinnacle_ft_over15_odd"/>
-    <tableColumn id="103" name="avg_pinnacle_ft_over25_odd"/>
-    <tableColumn id="104" name="avg_pinnacle_ft_over35_odd"/>
+    <tableColumn id="96" name="avg_pinnacle_1st_half_over05_odd"/>
+    <tableColumn id="97" name="avg_pinnacle_1st_half_over15_odd"/>
+    <tableColumn id="98" name="avg_pinnacle_1st_half_under05_odd"/>
+    <tableColumn id="99" name="avg_pinnacle_1st_half_under15_odd"/>
+    <tableColumn id="100" name="avg_pinnacle_corners_over_85_odd"/>
+    <tableColumn id="101" name="avg_pinnacle_corners_over_95_odd"/>
+    <tableColumn id="102" name="avg_pinnacle_corners_under_85_odd"/>
+    <tableColumn id="103" name="avg_pinnacle_corners_under_95_odd"/>
+    <tableColumn id="104" name="avg_pinnacle_ft_over15_odd"/>
+    <tableColumn id="105" name="avg_pinnacle_ft_over25_odd"/>
+    <tableColumn id="106" name="avg_pinnacle_ft_over35_odd"/>
+    <tableColumn id="107" name="total_avg_0_10_min_goals"/>
+    <tableColumn id="108" name="total_avg_2h_cards"/>
+    <tableColumn id="109" name="total_avg_2h_corners"/>
+    <tableColumn id="110" name="total_avg_attacks"/>
+    <tableColumn id="111" name="total_avg_cards_0_10_min"/>
+    <tableColumn id="112" name="total_avg_cards_num"/>
+    <tableColumn id="113" name="total_avg_corners"/>
+    <tableColumn id="114" name="total_avg_corners_0_10_min"/>
+    <tableColumn id="115" name="total_avg_dangerous_attacks"/>
+    <tableColumn id="116" name="total_avg_fh_cards"/>
+    <tableColumn id="117" name="total_avg_fh_corners"/>
+    <tableColumn id="118" name="total_avg_fouls"/>
+    <tableColumn id="119" name="total_avg_freekicks"/>
+    <tableColumn id="120" name="total_avg_goalkicks"/>
+    <tableColumn id="121" name="total_avg_penalties_won"/>
+    <tableColumn id="122" name="total_avg_penalty_goals"/>
+    <tableColumn id="123" name="total_avg_penalty_missed"/>
+    <tableColumn id="124" name="total_avg_possession"/>
+    <tableColumn id="125" name="total_avg_red_cards"/>
+    <tableColumn id="126" name="total_avg_shots"/>
+    <tableColumn id="127" name="total_avg_shotsOffTarget"/>
+    <tableColumn id="128" name="total_avg_shotsOnTarget"/>
+    <tableColumn id="129" name="total_avg_throwins"/>
+    <tableColumn id="130" name="total_avg_xg"/>
+    <tableColumn id="131" name="total_avg_yellow_cards"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -538,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CZ13"/>
+  <dimension ref="A1:EA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15.6" customWidth="1" min="1" max="1"/>
@@ -637,14 +664,41 @@
     <col width="24" customWidth="1" min="94" max="94"/>
     <col width="24" customWidth="1" min="95" max="95"/>
     <col width="40.8" customWidth="1" min="96" max="96"/>
-    <col width="42" customWidth="1" min="97" max="97"/>
-    <col width="40.8" customWidth="1" min="98" max="98"/>
-    <col width="40.8" customWidth="1" min="99" max="99"/>
-    <col width="42" customWidth="1" min="100" max="100"/>
-    <col width="42" customWidth="1" min="101" max="101"/>
-    <col width="33.6" customWidth="1" min="102" max="102"/>
-    <col width="33.6" customWidth="1" min="103" max="103"/>
+    <col width="40.8" customWidth="1" min="97" max="97"/>
+    <col width="42" customWidth="1" min="98" max="98"/>
+    <col width="42" customWidth="1" min="99" max="99"/>
+    <col width="40.8" customWidth="1" min="100" max="100"/>
+    <col width="40.8" customWidth="1" min="101" max="101"/>
+    <col width="42" customWidth="1" min="102" max="102"/>
+    <col width="42" customWidth="1" min="103" max="103"/>
     <col width="33.6" customWidth="1" min="104" max="104"/>
+    <col width="33.6" customWidth="1" min="105" max="105"/>
+    <col width="33.6" customWidth="1" min="106" max="106"/>
+    <col width="31.2" customWidth="1" min="107" max="107"/>
+    <col width="24" customWidth="1" min="108" max="108"/>
+    <col width="26.4" customWidth="1" min="109" max="109"/>
+    <col width="22.8" customWidth="1" min="110" max="110"/>
+    <col width="31.2" customWidth="1" min="111" max="111"/>
+    <col width="25.2" customWidth="1" min="112" max="112"/>
+    <col width="22.8" customWidth="1" min="113" max="113"/>
+    <col width="33.6" customWidth="1" min="114" max="114"/>
+    <col width="34.8" customWidth="1" min="115" max="115"/>
+    <col width="24" customWidth="1" min="116" max="116"/>
+    <col width="26.4" customWidth="1" min="117" max="117"/>
+    <col width="20.4" customWidth="1" min="118" max="118"/>
+    <col width="25.2" customWidth="1" min="119" max="119"/>
+    <col width="25.2" customWidth="1" min="120" max="120"/>
+    <col width="30" customWidth="1" min="121" max="121"/>
+    <col width="30" customWidth="1" min="122" max="122"/>
+    <col width="31.2" customWidth="1" min="123" max="123"/>
+    <col width="26.4" customWidth="1" min="124" max="124"/>
+    <col width="25.2" customWidth="1" min="125" max="125"/>
+    <col width="20.4" customWidth="1" min="126" max="126"/>
+    <col width="31.2" customWidth="1" min="127" max="127"/>
+    <col width="30" customWidth="1" min="128" max="128"/>
+    <col width="24" customWidth="1" min="129" max="129"/>
+    <col width="16.8" customWidth="1" min="130" max="130"/>
+    <col width="28.8" customWidth="1" min="131" max="131"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1125,47 +1179,182 @@
       </c>
       <c r="CR1" s="1" t="inlineStr">
         <is>
+          <t>avg_pinnacle_1st_half_over05_odd</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>avg_pinnacle_1st_half_under05_odd</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CW1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CX1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CY1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CZ1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="DA1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="DB1" s="1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_0_10_min_goals</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_cards</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_2h_corners</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_attacks</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_0_10_min</t>
+        </is>
+      </c>
+      <c r="DH1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_cards_num</t>
+        </is>
+      </c>
+      <c r="DI1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners</t>
+        </is>
+      </c>
+      <c r="DJ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_corners_0_10_min</t>
+        </is>
+      </c>
+      <c r="DK1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_dangerous_attacks</t>
+        </is>
+      </c>
+      <c r="DL1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_cards</t>
+        </is>
+      </c>
+      <c r="DM1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fh_corners</t>
+        </is>
+      </c>
+      <c r="DN1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_fouls</t>
+        </is>
+      </c>
+      <c r="DO1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_freekicks</t>
+        </is>
+      </c>
+      <c r="DP1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_goalkicks</t>
+        </is>
+      </c>
+      <c r="DQ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalties_won</t>
+        </is>
+      </c>
+      <c r="DR1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_goals</t>
+        </is>
+      </c>
+      <c r="DS1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_penalty_missed</t>
+        </is>
+      </c>
+      <c r="DT1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_possession</t>
+        </is>
+      </c>
+      <c r="DU1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_red_cards</t>
+        </is>
+      </c>
+      <c r="DV1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shots</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOffTarget</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_shotsOnTarget</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_throwins</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_xg</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>total_avg_yellow_cards</t>
         </is>
       </c>
     </row>
@@ -1176,13 +1365,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -1265,86 +1454,140 @@
       <c r="AE2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>59</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>13</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>0</v>
+      </c>
       <c r="BG2" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="BJ2" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BM2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>3</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BX2" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY2" t="n">
         <v>2.75</v>
@@ -1353,74 +1596,155 @@
         <v>2.94</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.56</v>
+        <v>4.03</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="CC2" t="inlineStr"/>
-      <c r="CD2" t="inlineStr"/>
+        <v>4.42</v>
+      </c>
+      <c r="CC2" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="CD2" t="n">
+        <v>7.24</v>
+      </c>
       <c r="CE2" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.51</v>
+        <v>2.3</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.22</v>
+        <v>3.44</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.35</v>
+        <v>2.24</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.02</v>
+        <v>2.91</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.26</v>
+        <v>2.19</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CR2" t="n">
-        <v>2.51</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="CR2" t="inlineStr"/>
       <c r="CS2" t="n">
-        <v>1.55</v>
+        <v>2.34</v>
       </c>
       <c r="CT2" t="inlineStr"/>
       <c r="CU2" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CX2" t="n">
-        <v>1.21</v>
-      </c>
+        <v>1.62</v>
+      </c>
+      <c r="CX2" t="inlineStr"/>
       <c r="CY2" t="n">
-        <v>1.69</v>
+        <v>2.24</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.67</v>
+        <v>1.18</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>3</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>83</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>5</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>36</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>12</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>9</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>37</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>6</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>17</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -1430,10 +1754,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -1442,49 +1766,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="n">
-        <v>106</v>
+        <v>114.5</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
-        <v>55</v>
+        <v>61.5</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="P3" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>3</v>
+        <v>8.5</v>
       </c>
       <c r="R3" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T3" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1496,28 +1820,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AA3" t="n">
-        <v>12</v>
+        <v>7.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>17</v>
+        <v>21.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.95</v>
+        <v>1.52</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -1547,34 +1871,34 @@
       <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BH3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
         <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BO3" t="n">
         <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BQ3" t="n">
         <v>3</v>
@@ -1583,10 +1907,10 @@
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT3" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
         <v>0</v>
@@ -1601,77 +1925,108 @@
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.25</v>
+        <v>4.15</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.51</v>
+        <v>4.46</v>
       </c>
       <c r="CC3" t="inlineStr"/>
       <c r="CD3" t="inlineStr"/>
       <c r="CE3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.88</v>
+        <v>3.74</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.45</v>
+        <v>2.28</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="CP3" t="n">
         <v>1.44</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CR3" t="n">
-        <v>2.21</v>
-      </c>
+        <v>2.16</v>
+      </c>
+      <c r="CR3" t="inlineStr"/>
       <c r="CS3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="n">
         <v>1.69</v>
       </c>
-      <c r="CT3" t="inlineStr"/>
-      <c r="CU3" t="inlineStr"/>
       <c r="CV3" t="inlineStr"/>
-      <c r="CW3" t="inlineStr"/>
-      <c r="CX3" t="n">
-        <v>1.15</v>
-      </c>
+      <c r="CW3" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.48</v>
+        <v>2.18</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.24</v>
-      </c>
+        <v>1.14</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
+      <c r="DH3" t="inlineStr"/>
+      <c r="DI3" t="inlineStr"/>
+      <c r="DJ3" t="inlineStr"/>
+      <c r="DK3" t="inlineStr"/>
+      <c r="DL3" t="inlineStr"/>
+      <c r="DM3" t="inlineStr"/>
+      <c r="DN3" t="inlineStr"/>
+      <c r="DO3" t="inlineStr"/>
+      <c r="DP3" t="inlineStr"/>
+      <c r="DQ3" t="inlineStr"/>
+      <c r="DR3" t="inlineStr"/>
+      <c r="DS3" t="inlineStr"/>
+      <c r="DT3" t="inlineStr"/>
+      <c r="DU3" t="inlineStr"/>
+      <c r="DV3" t="inlineStr"/>
+      <c r="DW3" t="inlineStr"/>
+      <c r="DX3" t="inlineStr"/>
+      <c r="DY3" t="inlineStr"/>
+      <c r="DZ3" t="inlineStr"/>
+      <c r="EA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1680,13 +2035,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1769,65 +2124,119 @@
       <c r="AE4" t="n">
         <v>1</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>84</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>19</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>2</v>
+      </c>
       <c r="BG4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BH4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BI4" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BM4" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN4" t="n">
         <v>2</v>
       </c>
       <c r="BO4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BP4" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
@@ -1839,7 +2248,7 @@
         <v>100</v>
       </c>
       <c r="BU4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV4" t="n">
         <v>0</v>
@@ -1857,70 +2266,155 @@
         <v>2.11</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.95</v>
+        <v>3.08</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="CC4" t="inlineStr"/>
-      <c r="CD4" t="inlineStr"/>
+        <v>3.4</v>
+      </c>
+      <c r="CC4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="CD4" t="n">
+        <v>3.38</v>
+      </c>
       <c r="CE4" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="CF4" t="n">
         <v>2.5</v>
       </c>
       <c r="CG4" t="n">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.97</v>
+        <v>1.94</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
       <c r="CN4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.51</v>
+        <v>2.64</v>
       </c>
       <c r="CR4" t="n">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="CS4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CT4" t="inlineStr"/>
-      <c r="CU4" t="inlineStr"/>
+        <v>2.58</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>1.52</v>
+      </c>
       <c r="CV4" t="inlineStr"/>
       <c r="CW4" t="inlineStr"/>
-      <c r="CX4" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CY4" t="n">
-        <v>1.68</v>
-      </c>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
       <c r="CZ4" t="n">
-        <v>2.59</v>
+        <v>1.21</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>98</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DI4" t="n">
+        <v>4</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="DL4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DM4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>5</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>8</v>
+      </c>
+      <c r="DQ4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DR4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="DU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" t="n">
+        <v>9</v>
+      </c>
+      <c r="DW4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DX4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DY4" t="n">
+        <v>20</v>
+      </c>
+      <c r="DZ4" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="EA4" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="5">
@@ -1930,10 +2424,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -1945,10 +2439,10 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H5" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -1957,34 +2451,34 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>6.5</v>
       </c>
       <c r="L5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>74</v>
+        <v>73.5</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="Q5" t="n">
-        <v>5</v>
+        <v>6.5</v>
       </c>
       <c r="R5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1996,25 +2490,25 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>67</v>
+        <v>65.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>13</v>
+        <v>9.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AB5" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>19</v>
+        <v>21.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="AE5" t="n">
         <v>1</v>
@@ -2047,131 +2541,162 @@
       <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BH5" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM5" t="n">
         <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="BQ5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>50</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CA5" t="n">
         <v>4</v>
       </c>
-      <c r="BR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="CB5" t="n">
-        <v>4.9</v>
+        <v>4.17</v>
       </c>
       <c r="CC5" t="inlineStr"/>
       <c r="CD5" t="inlineStr"/>
       <c r="CE5" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.4</v>
+        <v>3.14</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="CR5" t="n">
-        <v>2.46</v>
+        <v>1.34</v>
       </c>
       <c r="CS5" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CT5" t="inlineStr"/>
-      <c r="CU5" t="inlineStr"/>
+        <v>2.56</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>1.54</v>
+      </c>
       <c r="CV5" t="inlineStr"/>
       <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="CY5" t="n">
-        <v>1.61</v>
-      </c>
+      <c r="CX5" t="inlineStr"/>
+      <c r="CY5" t="inlineStr"/>
       <c r="CZ5" t="n">
-        <v>2.55</v>
-      </c>
+        <v>1.22</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr"/>
+      <c r="DE5" t="inlineStr"/>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
+      <c r="DH5" t="inlineStr"/>
+      <c r="DI5" t="inlineStr"/>
+      <c r="DJ5" t="inlineStr"/>
+      <c r="DK5" t="inlineStr"/>
+      <c r="DL5" t="inlineStr"/>
+      <c r="DM5" t="inlineStr"/>
+      <c r="DN5" t="inlineStr"/>
+      <c r="DO5" t="inlineStr"/>
+      <c r="DP5" t="inlineStr"/>
+      <c r="DQ5" t="inlineStr"/>
+      <c r="DR5" t="inlineStr"/>
+      <c r="DS5" t="inlineStr"/>
+      <c r="DT5" t="inlineStr"/>
+      <c r="DU5" t="inlineStr"/>
+      <c r="DV5" t="inlineStr"/>
+      <c r="DW5" t="inlineStr"/>
+      <c r="DX5" t="inlineStr"/>
+      <c r="DY5" t="inlineStr"/>
+      <c r="DZ5" t="inlineStr"/>
+      <c r="EA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2180,13 +2705,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -2269,68 +2794,122 @@
       <c r="AE6" t="n">
         <v>3</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>129</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1</v>
+      </c>
       <c r="BG6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BH6" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BP6" t="n">
         <v>3</v>
       </c>
-      <c r="BI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>2</v>
-      </c>
       <c r="BQ6" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BS6" t="n">
         <v>0</v>
@@ -2357,66 +2936,159 @@
         <v>2.83</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="CC6" t="inlineStr"/>
-      <c r="CD6" t="inlineStr"/>
+        <v>3.62</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>3.71</v>
+      </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.32</v>
+        <v>2.47</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="CH6" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="CO6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="CQ6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CV6" t="inlineStr"/>
+      <c r="CW6" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CX6" t="inlineStr"/>
+      <c r="CY6" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD6" t="n">
         <v>1.5</v>
       </c>
-      <c r="CI6" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CJ6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CK6" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CL6" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CM6" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="CN6" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CO6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CP6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CQ6" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CR6" t="inlineStr"/>
-      <c r="CS6" t="inlineStr"/>
-      <c r="CT6" t="inlineStr"/>
-      <c r="CU6" t="inlineStr"/>
-      <c r="CV6" t="inlineStr"/>
-      <c r="CW6" t="inlineStr"/>
-      <c r="CX6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CY6" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CZ6" t="n">
-        <v>2.79</v>
+      <c r="DE6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>115</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>64.5</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>11</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>8</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>53</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
+        <v>14</v>
+      </c>
+      <c r="DW6" t="n">
+        <v>10</v>
+      </c>
+      <c r="DX6" t="n">
+        <v>4</v>
+      </c>
+      <c r="DY6" t="n">
+        <v>25</v>
+      </c>
+      <c r="DZ6" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="EA6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -2426,41 +3098,95 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>153</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>9</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>96</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>11</v>
+      </c>
+      <c r="R7" t="n">
+        <v>4</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>75</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
@@ -2543,49 +3269,49 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="BI7" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>0</v>
       </c>
       <c r="BK7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN7" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BO7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BP7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV7" t="n">
         <v>0</v>
@@ -2594,15 +3320,19 @@
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>100</v>
-      </c>
-      <c r="BY7" t="inlineStr"/>
-      <c r="BZ7" t="inlineStr"/>
+        <v>50</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>1.41</v>
+      </c>
       <c r="CA7" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.37</v>
+        <v>4.31</v>
       </c>
       <c r="CC7" t="n">
         <v>2.9</v>
@@ -2611,62 +3341,143 @@
         <v>3.71</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="CG7" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.45</v>
+        <v>1.54</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="CJ7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CQ7" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CR7" t="inlineStr"/>
+      <c r="CS7" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CT7" t="inlineStr"/>
+      <c r="CU7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CV7" t="inlineStr"/>
+      <c r="CW7" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DA7" t="n">
         <v>1.57</v>
       </c>
-      <c r="CK7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CT7" t="inlineStr"/>
-      <c r="CU7" t="inlineStr"/>
-      <c r="CV7" t="inlineStr"/>
-      <c r="CW7" t="inlineStr"/>
-      <c r="CX7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CY7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>2.59</v>
+      <c r="DB7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI7" t="n">
+        <v>6</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>67</v>
+      </c>
+      <c r="DL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>63</v>
+      </c>
+      <c r="DU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DW7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DX7" t="n">
+        <v>9</v>
+      </c>
+      <c r="DY7" t="n">
+        <v>22</v>
+      </c>
+      <c r="DZ7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="EA7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -2676,13 +3487,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
@@ -2715,46 +3526,46 @@
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AL8" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="AM8" t="n">
         <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -2769,70 +3580,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="AZ8" t="n">
         <v>0</v>
       </c>
       <c r="BA8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH8" t="n">
         <v>7</v>
       </c>
-      <c r="BB8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>1</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>3</v>
-      </c>
       <c r="BI8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BO8" t="n">
         <v>1</v>
       </c>
       <c r="BP8" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="BQ8" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -2844,76 +3655,119 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="inlineStr"/>
       <c r="BZ8" t="inlineStr"/>
       <c r="CA8" t="n">
-        <v>3.35</v>
+        <v>3.28</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.57</v>
+        <v>3.62</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.69</v>
+        <v>2.45</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="CF8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CG8" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CH8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CK8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="CX8" t="n">
         <v>2.32</v>
       </c>
-      <c r="CG8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="CH8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CJ8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CK8" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CR8" t="inlineStr"/>
-      <c r="CS8" t="inlineStr"/>
-      <c r="CT8" t="inlineStr"/>
-      <c r="CU8" t="inlineStr"/>
-      <c r="CV8" t="inlineStr"/>
-      <c r="CW8" t="inlineStr"/>
-      <c r="CX8" t="n">
-        <v>1.22</v>
-      </c>
       <c r="CY8" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.79</v>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr"/>
+      <c r="DE8" t="inlineStr"/>
+      <c r="DF8" t="inlineStr"/>
+      <c r="DG8" t="inlineStr"/>
+      <c r="DH8" t="inlineStr"/>
+      <c r="DI8" t="inlineStr"/>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr"/>
+      <c r="DQ8" t="inlineStr"/>
+      <c r="DR8" t="inlineStr"/>
+      <c r="DS8" t="inlineStr"/>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
+      <c r="DZ8" t="inlineStr"/>
+      <c r="EA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2922,13 +3776,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -3011,41 +3865,95 @@
       <c r="AE9" t="n">
         <v>2</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>20</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2</v>
+      </c>
       <c r="BG9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BI9" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ9" t="n">
         <v>1</v>
@@ -3054,22 +3962,22 @@
         <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BO9" t="n">
         <v>1</v>
       </c>
       <c r="BP9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
@@ -3078,7 +3986,7 @@
         <v>100</v>
       </c>
       <c r="BT9" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU9" t="n">
         <v>0</v>
@@ -3090,7 +3998,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>1.75</v>
@@ -3099,78 +4007,163 @@
         <v>1.83</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="CC9" t="inlineStr"/>
-      <c r="CD9" t="inlineStr"/>
+        <v>3.96</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="CD9" t="n">
+        <v>5.59</v>
+      </c>
       <c r="CE9" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.34</v>
+        <v>3.28</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CM9" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="CN9" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="CR9" t="n">
-        <v>2.51</v>
+        <v>1.34</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT9" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CV9" t="n">
         <v>1.45</v>
       </c>
-      <c r="CU9" t="n">
+      <c r="CW9" t="n">
         <v>1.75</v>
       </c>
-      <c r="CV9" t="n">
+      <c r="CX9" t="n">
         <v>2.59</v>
       </c>
-      <c r="CW9" t="n">
+      <c r="CY9" t="n">
         <v>2.04</v>
       </c>
-      <c r="CX9" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CY9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="CZ9" t="n">
-        <v>2.61</v>
+        <v>1.22</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="DC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>13</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>8</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>49</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>5</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>4</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>21</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="EA9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -3180,13 +4173,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -3222,210 +4215,237 @@
         <v>1</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AN10" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AU10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ10" t="n">
         <v>5</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>51</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>8</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>2</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BU10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BV10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BW10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BX10" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="inlineStr"/>
       <c r="BZ10" t="inlineStr"/>
       <c r="CA10" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.59</v>
+        <v>4</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.41</v>
+        <v>3.36</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.38</v>
+        <v>3.51</v>
       </c>
       <c r="CE10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CK10" t="n">
         <v>1.3</v>
       </c>
-      <c r="CF10" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.29</v>
-      </c>
       <c r="CL10" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="CM10" t="n">
-        <v>3.02</v>
+        <v>2.9</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="CR10" t="n">
-        <v>2.51</v>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="CR10" t="inlineStr"/>
       <c r="CS10" t="n">
-        <v>1.55</v>
+        <v>2.37</v>
       </c>
       <c r="CT10" t="inlineStr"/>
       <c r="CU10" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="CV10" t="inlineStr"/>
       <c r="CW10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>1.21</v>
-      </c>
+        <v>1.62</v>
+      </c>
+      <c r="CX10" t="inlineStr"/>
       <c r="CY10" t="n">
-        <v>1.69</v>
+        <v>2.22</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.67</v>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="DC10" t="inlineStr"/>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+      <c r="DH10" t="inlineStr"/>
+      <c r="DI10" t="inlineStr"/>
+      <c r="DJ10" t="inlineStr"/>
+      <c r="DK10" t="inlineStr"/>
+      <c r="DL10" t="inlineStr"/>
+      <c r="DM10" t="inlineStr"/>
+      <c r="DN10" t="inlineStr"/>
+      <c r="DO10" t="inlineStr"/>
+      <c r="DP10" t="inlineStr"/>
+      <c r="DQ10" t="inlineStr"/>
+      <c r="DR10" t="inlineStr"/>
+      <c r="DS10" t="inlineStr"/>
+      <c r="DT10" t="inlineStr"/>
+      <c r="DU10" t="inlineStr"/>
+      <c r="DV10" t="inlineStr"/>
+      <c r="DW10" t="inlineStr"/>
+      <c r="DX10" t="inlineStr"/>
+      <c r="DY10" t="inlineStr"/>
+      <c r="DZ10" t="inlineStr"/>
+      <c r="EA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3434,41 +4454,95 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>106</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>75</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>-1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>13</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
       <c r="AF11" t="n">
         <v>0</v>
       </c>
@@ -3554,7 +4628,7 @@
         <v>3</v>
       </c>
       <c r="BH11" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BI11" t="n">
         <v>3</v>
@@ -3578,10 +4652,10 @@
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BR11" t="n">
         <v>100</v>
@@ -3604,13 +4678,17 @@
       <c r="BX11" t="n">
         <v>0</v>
       </c>
-      <c r="BY11" t="inlineStr"/>
-      <c r="BZ11" t="inlineStr"/>
+      <c r="BY11" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>1.65</v>
+      </c>
       <c r="CA11" t="n">
-        <v>4.25</v>
+        <v>3.88</v>
       </c>
       <c r="CB11" t="n">
-        <v>4.51</v>
+        <v>4.26</v>
       </c>
       <c r="CC11" t="n">
         <v>4.6</v>
@@ -3619,62 +4697,143 @@
         <v>5.15</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.88</v>
+        <v>3.55</v>
       </c>
       <c r="CH11" t="n">
         <v>1.7</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="CL11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="CU11" t="n">
         <v>1.6</v>
       </c>
-      <c r="CM11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CT11" t="inlineStr"/>
-      <c r="CU11" t="inlineStr"/>
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="CY11" t="n">
-        <v>1.48</v>
-      </c>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
       <c r="CZ11" t="n">
-        <v>2.24</v>
+        <v>1.19</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>88</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>1</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>4</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>9</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>4</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>13</v>
+      </c>
+      <c r="DZ11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="EA11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -3684,41 +4843,95 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>85</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>49</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>17</v>
+      </c>
+      <c r="R12" t="n">
+        <v>10</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>40</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>3</v>
+      </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
@@ -3801,13 +5014,13 @@
         <v>2</v>
       </c>
       <c r="BG12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BH12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="BJ12" t="n">
         <v>1</v>
@@ -3816,22 +5029,22 @@
         <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BM12" t="n">
         <v>1</v>
       </c>
       <c r="BN12" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="BO12" t="n">
         <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BQ12" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
@@ -3840,7 +5053,7 @@
         <v>100</v>
       </c>
       <c r="BT12" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
         <v>0</v>
@@ -3854,13 +5067,17 @@
       <c r="BX12" t="n">
         <v>100</v>
       </c>
-      <c r="BY12" t="inlineStr"/>
-      <c r="BZ12" t="inlineStr"/>
+      <c r="BY12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>3.19</v>
+      </c>
       <c r="CA12" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.91</v>
+        <v>3.79</v>
       </c>
       <c r="CC12" t="n">
         <v>3.6</v>
@@ -3869,70 +5086,151 @@
         <v>4.15</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.34</v>
+        <v>3.17</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.53</v>
+        <v>1.48</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="CM12" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.28</v>
+        <v>2.58</v>
       </c>
       <c r="CR12" t="n">
-        <v>2.51</v>
+        <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>1.55</v>
+        <v>2.66</v>
       </c>
       <c r="CT12" t="n">
-        <v>1.45</v>
+        <v>3.19</v>
       </c>
       <c r="CU12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CV12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CW12" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="CX12" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="CY12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="CZ12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DA12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DB12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DE12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DF12" t="n">
+        <v>90.5</v>
+      </c>
+      <c r="DG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DI12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="DJ12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK12" t="n">
+        <v>58.5</v>
+      </c>
+      <c r="DL12" t="n">
+        <v>1</v>
+      </c>
+      <c r="DM12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>14</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>10</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DX12" t="n">
+        <v>5</v>
+      </c>
+      <c r="DY12" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="DZ12" t="n">
         <v>1.75</v>
       </c>
-      <c r="CV12" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="CW12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="CX12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CY12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CZ12" t="n">
-        <v>2.61</v>
+      <c r="EA12" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -3942,41 +5240,95 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>124</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>60</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>10</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>54</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
@@ -4062,7 +5414,7 @@
         <v>0</v>
       </c>
       <c r="BH13" t="n">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
@@ -4086,10 +5438,10 @@
         <v>0</v>
       </c>
       <c r="BP13" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
@@ -4112,13 +5464,17 @@
       <c r="BX13" t="n">
         <v>0</v>
       </c>
-      <c r="BY13" t="inlineStr"/>
-      <c r="BZ13" t="inlineStr"/>
+      <c r="BY13" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>2.03</v>
+      </c>
       <c r="CA13" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="CB13" t="n">
-        <v>4.9</v>
+        <v>4.28</v>
       </c>
       <c r="CC13" t="n">
         <v>7.65</v>
@@ -4127,62 +5483,147 @@
         <v>7.56</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.4</v>
+        <v>3.22</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.55</v>
+        <v>1.49</v>
       </c>
       <c r="CI13" t="n">
-        <v>1.95</v>
+        <v>2.09</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.52</v>
+        <v>2.74</v>
       </c>
       <c r="CR13" t="n">
-        <v>2.46</v>
+        <v>1.4</v>
       </c>
       <c r="CS13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CT13" t="inlineStr"/>
-      <c r="CU13" t="inlineStr"/>
+        <v>2.7</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.5</v>
+      </c>
       <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="inlineStr"/>
-      <c r="CX13" t="n">
-        <v>1.2</v>
-      </c>
+      <c r="CW13" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CX13" t="inlineStr"/>
       <c r="CY13" t="n">
-        <v>1.61</v>
+        <v>2.07</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.55</v>
+        <v>1.25</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>106</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>13</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>7</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>4</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>3</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>22</v>
+      </c>
+      <c r="DZ13" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="EA13" t="n">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -702,657 +690,657 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>team_name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>total_games</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>home_games</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>away_games</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>home_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>home_avg_2h_cards</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>home_avg_2h_corners</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>home_avg_attacks</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>home_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>home_avg_cards_num</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>home_avg_corners</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>home_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>home_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>home_avg_fh_cards</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>home_avg_fh_corners</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>home_avg_fouls</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>home_avg_freekicks</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>home_avg_goalkicks</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>home_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>home_avg_goals_scored</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>home_avg_penalties_won</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>home_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>home_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>home_avg_possession</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>home_avg_red_cards</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>home_avg_shots</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>home_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>home_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>home_avg_throwins</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>home_avg_xg</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>home_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>away_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>away_avg_2h_cards</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>away_avg_2h_corners</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>away_avg_attacks</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>away_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>away_avg_cards_num</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>away_avg_corners</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>away_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>away_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>away_avg_fh_cards</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>away_avg_fh_corners</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>away_avg_fouls</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>away_avg_freekicks</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>away_avg_goalkicks</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>away_avg_goals_conceded</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>away_avg_goals_scored</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>away_avg_penalties_won</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>away_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>away_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>away_avg_possession</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>away_avg_red_cards</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>away_avg_shots</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>away_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>away_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>away_avg_throwins</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>away_avg_xg</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>away_avg_yellow_cards</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>totalGoalCount</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>totalCornerCount</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>overallGoalCount</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>ht_goals_team_a</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>ht_goals_team_b</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>goals_2hg_team_a</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>goals_2hg_team_b</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>GoalCount_2hg</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>HTGoalCount</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>corner_fh_count</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>corner_2h_count</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>over05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>over15</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>over25</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>over35</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>over45</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>over55</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>btts</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>avg_odds_ft_1</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_1_odd</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>avg_odds_ft_x</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_x_odd</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>avg_odds_ft_2</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_2_odd</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over05</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_over15</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under05</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>avg_odds_1st_half_under15</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>avg_odds_btts_no</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>avg_odds_btts_yes</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_85</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>avg_odds_corners_over_95</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_85</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>avg_odds_corners_under_95</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over15</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over25</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>avg_odds_ft_over35</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over05_odd</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_over15_odd</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under05_odd</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>avg_pinnacle_1st_half_under15_odd</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_85_odd</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_over_95_odd</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_85_odd</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>avg_pinnacle_corners_under_95_odd</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over15_odd</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over25_odd</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>avg_pinnacle_ft_over35_odd</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>total_avg_0_10_min_goals</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>total_avg_2h_cards</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>total_avg_2h_corners</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>total_avg_attacks</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>total_avg_cards_0_10_min</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>total_avg_cards_num</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>total_avg_corners</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>total_avg_corners_0_10_min</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>total_avg_dangerous_attacks</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>total_avg_fh_cards</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>total_avg_fh_corners</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>total_avg_fouls</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>total_avg_freekicks</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>total_avg_goalkicks</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>total_avg_penalties_won</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>total_avg_penalty_goals</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>total_avg_penalty_missed</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>total_avg_possession</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>total_avg_red_cards</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>total_avg_shots</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>total_avg_shotsOffTarget</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>total_avg_shotsOnTarget</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>total_avg_throwins</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>total_avg_xg</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>total_avg_yellow_cards</t>
         </is>
@@ -1365,61 +1353,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>2.75</v>
       </c>
       <c r="H2" t="n">
-        <v>107</v>
+        <v>89.75</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>36.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P2" t="n">
-        <v>13</v>
+        <v>9.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="R2" t="n">
         <v>8</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1431,76 +1419,76 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>49</v>
+        <v>43.25</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>12</v>
+        <v>9.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>7</v>
+        <v>5.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="AC2" t="n">
         <v>21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.46</v>
+        <v>1.14</v>
       </c>
       <c r="AE2" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>69</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32.67</v>
+      </c>
+      <c r="AO2" t="n">
         <v>1</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>59</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
       <c r="AP2" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>11</v>
+        <v>15.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>1.67</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>7.33</v>
       </c>
       <c r="AT2" t="n">
         <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1512,206 +1500,210 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="AZ2" t="n">
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>7</v>
+        <v>7.67</v>
       </c>
       <c r="BB2" t="n">
         <v>5</v>
       </c>
       <c r="BC2" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="BD2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.77</v>
+        <v>0.91</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.5</v>
+        <v>10.14</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL2" t="n">
         <v>1</v>
       </c>
-      <c r="BL2" t="n">
-        <v>0.5</v>
-      </c>
       <c r="BM2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BN2" t="n">
         <v>2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.5</v>
+        <v>4.71</v>
       </c>
       <c r="BQ2" t="n">
-        <v>3</v>
+        <v>5.43</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>50</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>28.57</v>
       </c>
       <c r="BV2" t="n">
-        <v>50</v>
+        <v>28.57</v>
       </c>
       <c r="BW2" t="n">
-        <v>50</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>50</v>
+        <v>42.86</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.75</v>
+        <v>3.51</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.94</v>
+        <v>3.68</v>
       </c>
       <c r="CA2" t="n">
-        <v>4.03</v>
+        <v>3.76</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.42</v>
+        <v>4.09</v>
       </c>
       <c r="CC2" t="n">
-        <v>7.64</v>
+        <v>4.52</v>
       </c>
       <c r="CD2" t="n">
-        <v>7.24</v>
+        <v>4.72</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.44</v>
+        <v>3.27</v>
       </c>
       <c r="CH2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="CI2" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CJ2" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CK2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CM2" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CN2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CO2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="CQ2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CR2" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS2" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="CT2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CU2" t="n">
         <v>1.58</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="CJ2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CK2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="CL2" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CM2" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="CN2" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CO2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CP2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CQ2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CR2" t="inlineStr"/>
-      <c r="CS2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CT2" t="inlineStr"/>
-      <c r="CU2" t="n">
-        <v>1.64</v>
       </c>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="CX2" t="inlineStr"/>
       <c r="CY2" t="n">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="DB2" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.5</v>
+        <v>1.57</v>
       </c>
       <c r="DE2" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="DF2" t="n">
-        <v>83</v>
+        <v>80.86</v>
       </c>
       <c r="DG2" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.5</v>
+        <v>2.14</v>
       </c>
       <c r="DI2" t="n">
-        <v>5</v>
+        <v>3.71</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DK2" t="n">
-        <v>36</v>
+        <v>34.86</v>
       </c>
       <c r="DL2" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0.5</v>
+        <v>1.57</v>
       </c>
       <c r="DN2" t="n">
-        <v>12</v>
+        <v>11.86</v>
       </c>
       <c r="DO2" t="n">
-        <v>5</v>
+        <v>2.57</v>
       </c>
       <c r="DP2" t="n">
-        <v>9</v>
+        <v>7.71</v>
       </c>
       <c r="DQ2" t="n">
         <v>0</v>
@@ -1723,28 +1715,28 @@
         <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>37</v>
+        <v>41.86</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>9.5</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DW2" t="n">
-        <v>6</v>
+        <v>5.43</v>
       </c>
       <c r="DX2" t="n">
-        <v>3.5</v>
+        <v>3.29</v>
       </c>
       <c r="DY2" t="n">
-        <v>17</v>
+        <v>20.14</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.5</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="3">
@@ -1754,58 +1746,58 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>1.25</v>
       </c>
       <c r="G3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H3" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>1.5</v>
       </c>
-      <c r="H3" t="n">
-        <v>114.5</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.5</v>
-      </c>
       <c r="K3" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>61.5</v>
+        <v>62</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O3" t="n">
-        <v>3.5</v>
+        <v>2.75</v>
       </c>
       <c r="P3" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>8.5</v>
+        <v>1.75</v>
       </c>
       <c r="R3" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="T3" t="n">
         <v>1.5</v>
@@ -1820,100 +1812,154 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>58</v>
+        <v>54.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z3" t="n">
-        <v>12</v>
+        <v>13.25</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.5</v>
+        <v>20.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.52</v>
+        <v>1.62</v>
       </c>
       <c r="AE3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
         <v>0.5</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+      <c r="AH3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>90.25</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>24.75</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1</v>
+      </c>
       <c r="BG3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BH3" t="n">
-        <v>8</v>
+        <v>10.88</v>
       </c>
       <c r="BI3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
         <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="BM3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
         <v>1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BP3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>3</v>
+        <v>4.88</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1922,111 +1968,169 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="BZ3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="CB3" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="CC3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CD3" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CE3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="CF3" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CI3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="CJ3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CK3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="CL3" t="n">
         <v>1.64</v>
       </c>
-      <c r="CA3" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="CB3" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="CC3" t="inlineStr"/>
-      <c r="CD3" t="inlineStr"/>
-      <c r="CE3" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CF3" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="CG3" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="CJ3" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CK3" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="CL3" t="n">
-        <v>1.62</v>
-      </c>
       <c r="CM3" t="n">
-        <v>2.91</v>
+        <v>2.99</v>
       </c>
       <c r="CN3" t="n">
         <v>2.28</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.11</v>
+        <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="CR3" t="inlineStr"/>
+        <v>2.52</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.36</v>
+      </c>
       <c r="CS3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CT3" t="inlineStr"/>
+        <v>2.46</v>
+      </c>
+      <c r="CT3" t="n">
+        <v>3.22</v>
+      </c>
       <c r="CU3" t="n">
-        <v>1.69</v>
+        <v>1.6</v>
       </c>
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>2.18</v>
+        <v>2.33</v>
       </c>
       <c r="CZ3" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="DC3" t="inlineStr"/>
-      <c r="DD3" t="inlineStr"/>
-      <c r="DE3" t="inlineStr"/>
-      <c r="DF3" t="inlineStr"/>
-      <c r="DG3" t="inlineStr"/>
-      <c r="DH3" t="inlineStr"/>
-      <c r="DI3" t="inlineStr"/>
-      <c r="DJ3" t="inlineStr"/>
-      <c r="DK3" t="inlineStr"/>
-      <c r="DL3" t="inlineStr"/>
-      <c r="DM3" t="inlineStr"/>
-      <c r="DN3" t="inlineStr"/>
-      <c r="DO3" t="inlineStr"/>
-      <c r="DP3" t="inlineStr"/>
-      <c r="DQ3" t="inlineStr"/>
-      <c r="DR3" t="inlineStr"/>
-      <c r="DS3" t="inlineStr"/>
-      <c r="DT3" t="inlineStr"/>
-      <c r="DU3" t="inlineStr"/>
-      <c r="DV3" t="inlineStr"/>
-      <c r="DW3" t="inlineStr"/>
-      <c r="DX3" t="inlineStr"/>
-      <c r="DY3" t="inlineStr"/>
-      <c r="DZ3" t="inlineStr"/>
-      <c r="EA3" t="inlineStr"/>
+        <v>2.57</v>
+      </c>
+      <c r="DC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD3" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DI3" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>58.25</v>
+      </c>
+      <c r="DL3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DM3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="DN3" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>8.619999999999999</v>
+      </c>
+      <c r="DQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="DW3" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="DX3" t="n">
+        <v>4</v>
+      </c>
+      <c r="DY3" t="n">
+        <v>22.62</v>
+      </c>
+      <c r="DZ3" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="EA3" t="n">
+        <v>1.12</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2035,58 +2139,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="H4" t="n">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="K4" t="n">
-        <v>4</v>
+        <v>2.33</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>70</v>
+        <v>52.33</v>
       </c>
       <c r="N4" t="n">
         <v>1</v>
       </c>
       <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>9</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="S4" t="n">
         <v>2</v>
-      </c>
-      <c r="P4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
@@ -2101,220 +2205,220 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49</v>
+        <v>46.33</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AA4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AB4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.74</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AH4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AK4" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AL4" t="n">
         <v>4</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AN4" t="n">
-        <v>23</v>
+        <v>38.6</v>
       </c>
       <c r="AO4" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AP4" t="n">
         <v>2</v>
       </c>
-      <c r="AP4" t="n">
-        <v>1</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR4" t="n">
-        <v>9</v>
+        <v>1.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT4" t="n">
         <v>2</v>
       </c>
       <c r="AU4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BK4" t="n">
         <v>1</v>
       </c>
-      <c r="AV4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>19</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>2</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK4" t="n">
+      <c r="BL4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BN4" t="n">
         <v>1.5</v>
       </c>
-      <c r="BL4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>2</v>
-      </c>
       <c r="BO4" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="BP4" t="n">
-        <v>2.5</v>
+        <v>4.12</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.5</v>
+        <v>5.5</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="BU4" t="n">
-        <v>50</v>
+        <v>62.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.17</v>
+        <v>2.68</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.11</v>
+        <v>2.82</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.08</v>
+        <v>3.55</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.4</v>
+        <v>3.87</v>
       </c>
       <c r="CC4" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.38</v>
+        <v>3.04</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CG4" t="n">
-        <v>2.94</v>
+        <v>3.13</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.59</v>
+        <v>2.87</v>
       </c>
       <c r="CN4" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CR4" t="n">
         <v>1.34</v>
@@ -2323,98 +2427,102 @@
         <v>2.58</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="inlineStr"/>
+      <c r="CW4" t="n">
+        <v>1.64</v>
+      </c>
       <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="inlineStr"/>
+      <c r="CY4" t="n">
+        <v>2.22</v>
+      </c>
       <c r="CZ4" t="n">
         <v>1.21</v>
       </c>
       <c r="DA4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="DB4" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="DC4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DD4" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="DE4" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="DF4" t="n">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
       <c r="DI4" t="n">
-        <v>4</v>
+        <v>3.37</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DK4" t="n">
-        <v>46.5</v>
+        <v>43.75</v>
       </c>
       <c r="DL4" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="DN4" t="n">
-        <v>7.5</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DO4" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="DP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>42.5</v>
+        <v>47</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="DW4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="DX4" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="DY4" t="n">
-        <v>20</v>
+        <v>16.75</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="EA4" t="n">
-        <v>1.5</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="5">
@@ -2424,166 +2532,220 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>9</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R5" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>50.75</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
-        <v>5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>106</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1</v>
-      </c>
-      <c r="M5" t="n">
-        <v>73.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>65.5</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
+      <c r="AV5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
         <v>9.5</v>
       </c>
-      <c r="AA5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+      <c r="BB5" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>1.25</v>
+      </c>
       <c r="BG5" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="BH5" t="n">
-        <v>10</v>
+        <v>10.33</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BL5" t="n">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
       <c r="BN5" t="n">
         <v>1</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.5</v>
+        <v>1.22</v>
       </c>
       <c r="BP5" t="n">
-        <v>2.5</v>
+        <v>3.67</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.5</v>
+        <v>5</v>
       </c>
       <c r="BR5" t="n">
-        <v>50</v>
+        <v>88.89</v>
       </c>
       <c r="BS5" t="n">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="BT5" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>22.22</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2592,111 +2754,173 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.78</v>
+        <v>1.72</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="CA5" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="CC5" t="inlineStr"/>
-      <c r="CD5" t="inlineStr"/>
+        <v>4.07</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>2</v>
+      </c>
       <c r="CE5" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.3</v>
+        <v>2.54</v>
       </c>
       <c r="CG5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="CO5" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="CP5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CQ5" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="CT5" t="n">
         <v>3.14</v>
       </c>
-      <c r="CH5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CI5" t="n">
+      <c r="CU5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CX5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CY5" t="n">
         <v>2.12</v>
       </c>
-      <c r="CJ5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CK5" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CM5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CN5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="CO5" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CQ5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="CR5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="CT5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="CU5" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="CV5" t="inlineStr"/>
-      <c r="CW5" t="inlineStr"/>
-      <c r="CX5" t="inlineStr"/>
-      <c r="CY5" t="inlineStr"/>
       <c r="CZ5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="DD5" t="n">
         <v>1.22</v>
       </c>
-      <c r="DA5" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="DB5" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="DC5" t="inlineStr"/>
-      <c r="DD5" t="inlineStr"/>
-      <c r="DE5" t="inlineStr"/>
-      <c r="DF5" t="inlineStr"/>
-      <c r="DG5" t="inlineStr"/>
-      <c r="DH5" t="inlineStr"/>
-      <c r="DI5" t="inlineStr"/>
-      <c r="DJ5" t="inlineStr"/>
-      <c r="DK5" t="inlineStr"/>
-      <c r="DL5" t="inlineStr"/>
-      <c r="DM5" t="inlineStr"/>
-      <c r="DN5" t="inlineStr"/>
-      <c r="DO5" t="inlineStr"/>
-      <c r="DP5" t="inlineStr"/>
-      <c r="DQ5" t="inlineStr"/>
-      <c r="DR5" t="inlineStr"/>
-      <c r="DS5" t="inlineStr"/>
-      <c r="DT5" t="inlineStr"/>
-      <c r="DU5" t="inlineStr"/>
-      <c r="DV5" t="inlineStr"/>
-      <c r="DW5" t="inlineStr"/>
-      <c r="DX5" t="inlineStr"/>
-      <c r="DY5" t="inlineStr"/>
-      <c r="DZ5" t="inlineStr"/>
-      <c r="EA5" t="inlineStr"/>
+      <c r="DE5" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>89.44</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DI5" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>59.11</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DM5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DN5" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DR5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="DU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV5" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="DW5" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="DX5" t="n">
+        <v>5</v>
+      </c>
+      <c r="DY5" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="DZ5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="EA5" t="n">
+        <v>1.44</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2705,106 +2929,106 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>8</v>
+      </c>
+      <c r="C6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G6" t="n">
         <v>2</v>
       </c>
-      <c r="C6" t="n">
+      <c r="H6" t="n">
+        <v>97</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>62</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
+      <c r="P6" t="n">
+        <v>14.67</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>5</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" t="n">
-        <v>101</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>61</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>11</v>
-      </c>
-      <c r="R6" t="n">
-        <v>6</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AA6" t="n">
-        <v>7</v>
+        <v>5.33</v>
       </c>
       <c r="AB6" t="n">
-        <v>3</v>
+        <v>3.67</v>
       </c>
       <c r="AC6" t="n">
-        <v>36</v>
+        <v>23.33</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AH6" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="AI6" t="n">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -2813,34 +3037,34 @@
         <v>1</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="AM6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AP6" t="n">
         <v>1</v>
       </c>
-      <c r="AN6" t="n">
-        <v>68</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>2</v>
-      </c>
       <c r="AQ6" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>11</v>
+        <v>3.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -2852,243 +3076,243 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46</v>
+        <v>45.2</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>12.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>14</v>
+        <v>16.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.98</v>
+        <v>1.39</v>
       </c>
       <c r="BF6" t="n">
         <v>1</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.5</v>
+        <v>2.38</v>
       </c>
       <c r="BH6" t="n">
-        <v>6.5</v>
+        <v>7.88</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.5</v>
+        <v>2.38</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.5</v>
+        <v>1.12</v>
       </c>
       <c r="BP6" t="n">
-        <v>3</v>
+        <v>4.38</v>
       </c>
       <c r="BQ6" t="n">
         <v>3.5</v>
       </c>
       <c r="BR6" t="n">
-        <v>50</v>
+        <v>87.5</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.46</v>
+        <v>3.23</v>
       </c>
       <c r="BZ6" t="n">
-        <v>2.83</v>
+        <v>3.51</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.48</v>
+        <v>3.73</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.62</v>
+        <v>3.93</v>
       </c>
       <c r="CC6" t="n">
-        <v>3.2</v>
+        <v>4.21</v>
       </c>
       <c r="CD6" t="n">
-        <v>3.71</v>
+        <v>4.65</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.47</v>
+        <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH6" t="n">
         <v>1.46</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="CK6" t="n">
         <v>1.4</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="CM6" t="n">
         <v>2.68</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.93</v>
+        <v>2.7</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="CV6" t="inlineStr"/>
       <c r="CW6" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CX6" t="inlineStr"/>
       <c r="CY6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CZ6" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DF6" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH6" t="n">
         <v>1.25</v>
       </c>
-      <c r="DA6" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="DB6" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="DC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DE6" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF6" t="n">
-        <v>115</v>
-      </c>
-      <c r="DG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>2</v>
-      </c>
       <c r="DI6" t="n">
-        <v>3</v>
+        <v>3.38</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="DK6" t="n">
-        <v>64.5</v>
+        <v>52.75</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
         <v>1</v>
       </c>
       <c r="DN6" t="n">
-        <v>11.5</v>
+        <v>12.13</v>
       </c>
       <c r="DO6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="DQ6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DR6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV6" t="n">
         <v>11</v>
       </c>
-      <c r="DP6" t="n">
-        <v>8</v>
-      </c>
-      <c r="DQ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT6" t="n">
-        <v>53</v>
-      </c>
-      <c r="DU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV6" t="n">
-        <v>14</v>
-      </c>
       <c r="DW6" t="n">
-        <v>10</v>
+        <v>7.12</v>
       </c>
       <c r="DX6" t="n">
-        <v>4</v>
+        <v>3.88</v>
       </c>
       <c r="DY6" t="n">
-        <v>25</v>
+        <v>19.12</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.64</v>
+        <v>1.35</v>
       </c>
       <c r="EA6" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="7">
@@ -3098,142 +3322,142 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>9</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>116.4</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M7" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P7" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>9</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="AD7" t="n">
         <v>2</v>
       </c>
-      <c r="C7" t="n">
+      <c r="AE7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>128.25</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AM7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H7" t="n">
-        <v>153</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>96</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P7" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>11</v>
-      </c>
-      <c r="R7" t="n">
-        <v>4</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>75</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>28</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>106</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0</v>
-      </c>
       <c r="AN7" t="n">
-        <v>38</v>
+        <v>71</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>3.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>5</v>
+        <v>9.75</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AS7" t="n">
-        <v>11</v>
+        <v>7.25</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>3</v>
+        <v>1.25</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3245,206 +3469,214 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BA7" t="n">
-        <v>12</v>
+        <v>12.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>7</v>
+        <v>5.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BH7" t="n">
-        <v>9.5</v>
+        <v>11.22</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="BK7" t="n">
-        <v>1</v>
+        <v>0.44</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.78</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="BO7" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP7" t="n">
-        <v>1</v>
+        <v>6.33</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.5</v>
+        <v>4.89</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>88.89</v>
       </c>
       <c r="BS7" t="n">
-        <v>50</v>
+        <v>77.78</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>50</v>
+        <v>22.22</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>55.56</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.35</v>
+        <v>1.74</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.41</v>
+        <v>1.77</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.72</v>
+        <v>3.84</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.31</v>
+        <v>4.15</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.9</v>
+        <v>2.03</v>
       </c>
       <c r="CD7" t="n">
-        <v>3.71</v>
+        <v>2.28</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.33</v>
+        <v>3.21</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="CL7" t="n">
         <v>1.9</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.66</v>
+        <v>2.59</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CR7" t="inlineStr"/>
+        <v>2.64</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>1.36</v>
+      </c>
       <c r="CS7" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CT7" t="inlineStr"/>
+        <v>2.57</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>3.24</v>
+      </c>
       <c r="CU7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CV7" t="inlineStr"/>
+        <v>1.54</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>1.53</v>
+      </c>
       <c r="CW7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CX7" t="inlineStr"/>
+        <v>1.74</v>
+      </c>
+      <c r="CX7" t="n">
+        <v>2.41</v>
+      </c>
       <c r="CY7" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.5</v>
+        <v>3.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>129.5</v>
+        <v>121.67</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.5</v>
+        <v>-0.22</v>
       </c>
       <c r="DH7" t="n">
-        <v>0</v>
+        <v>0.89</v>
       </c>
       <c r="DI7" t="n">
-        <v>6</v>
+        <v>7.56</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.5</v>
+        <v>1.22</v>
       </c>
       <c r="DK7" t="n">
-        <v>67</v>
+        <v>68.67</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="DN7" t="n">
-        <v>6.5</v>
+        <v>10.22</v>
       </c>
       <c r="DO7" t="n">
-        <v>5.5</v>
+        <v>3.11</v>
       </c>
       <c r="DP7" t="n">
-        <v>7.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
@@ -3456,28 +3688,28 @@
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>63</v>
+        <v>61.89</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DV7" t="n">
-        <v>15.5</v>
+        <v>15.11</v>
       </c>
       <c r="DW7" t="n">
-        <v>6.5</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>9</v>
+        <v>5.89</v>
       </c>
       <c r="DY7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="DZ7" t="n">
-        <v>2.1</v>
+        <v>1.87</v>
       </c>
       <c r="EA7" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="8">
@@ -3487,88 +3719,142 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>7</v>
+      </c>
+      <c r="C8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>99.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="n">
+      <c r="K8" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="M8" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="P8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>56.25</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>10.75</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE8" t="n">
         <v>2</v>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AH8" t="n">
         <v>3</v>
       </c>
-      <c r="AH8" t="n">
-        <v>2</v>
-      </c>
       <c r="AI8" t="n">
-        <v>69</v>
+        <v>76.67</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AN8" t="n">
-        <v>37.5</v>
+        <v>42.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AP8" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AQ8" t="n">
         <v>14</v>
       </c>
       <c r="AR8" t="n">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="AS8" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="AT8" t="n">
         <v>1</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.67</v>
       </c>
       <c r="AV8" t="n">
         <v>0</v>
@@ -3580,70 +3866,70 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>50</v>
+        <v>51.33</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.5</v>
+        <v>11.67</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="BC8" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="BD8" t="n">
-        <v>23.5</v>
+        <v>20.67</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BF8" t="n">
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="BG8" t="n">
         <v>2</v>
       </c>
       <c r="BH8" t="n">
-        <v>7</v>
+        <v>9.43</v>
       </c>
       <c r="BI8" t="n">
         <v>2</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="BO8" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>2.5</v>
+        <v>3.29</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>50</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>28.57</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -3655,119 +3941,173 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY8" t="inlineStr"/>
-      <c r="BZ8" t="inlineStr"/>
+        <v>57.14</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>2.68</v>
+      </c>
       <c r="CA8" t="n">
-        <v>3.28</v>
+        <v>3.52</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.62</v>
+        <v>3.8</v>
       </c>
       <c r="CC8" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="CD8" t="n">
-        <v>2.36</v>
+        <v>3.45</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.58</v>
+        <v>2.79</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="CH8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CI8" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="CJ8" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CK8" t="n">
         <v>1.46</v>
       </c>
-      <c r="CI8" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CJ8" t="n">
+      <c r="CL8" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="CM8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CN8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="CO8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="CP8" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="CQ8" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CS8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="CT8" t="n">
+        <v>3</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CV8" t="n">
         <v>1.57</v>
       </c>
-      <c r="CK8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CL8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="CM8" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="CN8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="CO8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CP8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CQ8" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="CR8" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="CT8" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="CU8" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="CV8" t="n">
-        <v>1.56</v>
-      </c>
       <c r="CW8" t="n">
-        <v>1.99</v>
+        <v>1.84</v>
       </c>
       <c r="CX8" t="n">
         <v>2.32</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="CZ8" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="DB8" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="DC8" t="inlineStr"/>
-      <c r="DD8" t="inlineStr"/>
-      <c r="DE8" t="inlineStr"/>
-      <c r="DF8" t="inlineStr"/>
-      <c r="DG8" t="inlineStr"/>
-      <c r="DH8" t="inlineStr"/>
-      <c r="DI8" t="inlineStr"/>
-      <c r="DJ8" t="inlineStr"/>
-      <c r="DK8" t="inlineStr"/>
-      <c r="DL8" t="inlineStr"/>
-      <c r="DM8" t="inlineStr"/>
-      <c r="DN8" t="inlineStr"/>
-      <c r="DO8" t="inlineStr"/>
-      <c r="DP8" t="inlineStr"/>
-      <c r="DQ8" t="inlineStr"/>
-      <c r="DR8" t="inlineStr"/>
-      <c r="DS8" t="inlineStr"/>
-      <c r="DT8" t="inlineStr"/>
-      <c r="DU8" t="inlineStr"/>
-      <c r="DV8" t="inlineStr"/>
-      <c r="DW8" t="inlineStr"/>
-      <c r="DX8" t="inlineStr"/>
-      <c r="DY8" t="inlineStr"/>
-      <c r="DZ8" t="inlineStr"/>
-      <c r="EA8" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="DC8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DD8" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>89.72</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH8" t="n">
+        <v>3</v>
+      </c>
+      <c r="DI8" t="n">
+        <v>5.29</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>45.29</v>
+      </c>
+      <c r="DL8" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DM8" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DN8" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>6</v>
+      </c>
+      <c r="DQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="DW8" t="n">
+        <v>7.71</v>
+      </c>
+      <c r="DX8" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DY8" t="n">
+        <v>23.14</v>
+      </c>
+      <c r="DZ8" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="EA8" t="n">
+        <v>2.57</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3776,58 +4116,58 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H9" t="n">
+        <v>79.5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>75</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2</v>
-      </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M9" t="n">
-        <v>36</v>
+        <v>34.75</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>12.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>10.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
@@ -3842,88 +4182,88 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>49</v>
+        <v>47.5</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>7</v>
+        <v>7.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="AB9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1</v>
       </c>
-      <c r="AC9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>2</v>
-      </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>23</v>
+        <v>34.67</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>1.67</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>10.67</v>
       </c>
       <c r="AR9" t="n">
-        <v>14</v>
+        <v>1.33</v>
       </c>
       <c r="AS9" t="n">
-        <v>12</v>
+        <v>12.33</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>49</v>
+        <v>44.33</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -3938,58 +4278,58 @@
         <v>1</v>
       </c>
       <c r="BD9" t="n">
-        <v>20</v>
+        <v>19.67</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.44</v>
+        <v>0.52</v>
       </c>
       <c r="BF9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BH9" t="n">
-        <v>9</v>
+        <v>11.14</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BJ9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BN9" t="n">
         <v>1</v>
       </c>
-      <c r="BK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BO9" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="BP9" t="n">
-        <v>4</v>
+        <v>5.14</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0</v>
+        <v>4.57</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT9" t="n">
-        <v>50</v>
+        <v>28.57</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -3998,172 +4338,172 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>57.14</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.75</v>
+        <v>4.01</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.83</v>
+        <v>4.67</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.55</v>
+        <v>4.01</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.96</v>
+        <v>4.5</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.55</v>
+        <v>6.17</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.59</v>
+        <v>7.94</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.17</v>
+        <v>2.43</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.52</v>
+        <v>1.74</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="CM9" t="n">
-        <v>3.04</v>
+        <v>2.8</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.36</v>
+        <v>2.66</v>
       </c>
       <c r="CR9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.37</v>
+        <v>3.23</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="CV9" t="n">
         <v>1.45</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CX9" t="n">
         <v>2.59</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.71</v>
+        <v>2.86</v>
       </c>
       <c r="DC9" t="n">
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>2</v>
+        <v>0.86</v>
       </c>
       <c r="DE9" t="n">
-        <v>-0.5</v>
+        <v>1.29</v>
       </c>
       <c r="DF9" t="n">
-        <v>82.5</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="DG9" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="DH9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DI9" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>34.72</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>11.14</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>46.14</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="DZ9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="EA9" t="n">
         <v>1</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>13</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>8</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>49</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>5</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>4</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>21</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="EA9" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -4173,154 +4513,208 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="H10" t="n">
+        <v>83</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="K10" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M10" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="O10" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="P10" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="R10" t="n">
+        <v>9</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>28.33</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2</v>
       </c>
-      <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="n">
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AI10" t="n">
-        <v>78.5</v>
+        <v>84.8</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AN10" t="n">
-        <v>40</v>
+        <v>43.6</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>7.5</v>
+        <v>10.8</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="AS10" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.5</v>
+        <v>1.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>43.5</v>
+        <v>48.4</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
       <c r="BB10" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.5</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>21.5</v>
+        <v>22.2</v>
       </c>
       <c r="BE10" t="n">
         <v>1.38</v>
       </c>
       <c r="BF10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BG10" t="n">
         <v>2.5</v>
       </c>
-      <c r="BG10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BH10" t="n">
-        <v>8</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="BJ10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.5</v>
       </c>
-      <c r="BK10" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BL10" t="n">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.5</v>
+        <v>0.62</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="BO10" t="n">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>3</v>
+        <v>4.88</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5</v>
+        <v>4.38</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
@@ -4329,123 +4723,185 @@
         <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>50</v>
+        <v>37.5</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="BV10" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="BW10" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
-      </c>
-      <c r="BY10" t="inlineStr"/>
-      <c r="BZ10" t="inlineStr"/>
+        <v>37.5</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>2.11</v>
+      </c>
       <c r="CA10" t="n">
-        <v>3.8</v>
+        <v>3.66</v>
       </c>
       <c r="CB10" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="CC10" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="CD10" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="CE10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="CF10" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CG10" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="CH10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CI10" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="CJ10" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="CK10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CP10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="CQ10" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="CR10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS10" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="CT10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>84.12</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>44</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>11.37</v>
+      </c>
+      <c r="DO10" t="n">
         <v>4</v>
       </c>
-      <c r="CC10" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="CD10" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="CE10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="CF10" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="CG10" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="CH10" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CJ10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CK10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CL10" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="CM10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CQ10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="CR10" t="inlineStr"/>
-      <c r="CS10" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CT10" t="inlineStr"/>
-      <c r="CU10" t="n">
+      <c r="DP10" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>46.87</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="EA10" t="n">
         <v>1.62</v>
       </c>
-      <c r="CV10" t="inlineStr"/>
-      <c r="CW10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="CX10" t="inlineStr"/>
-      <c r="CY10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="DC10" t="inlineStr"/>
-      <c r="DD10" t="inlineStr"/>
-      <c r="DE10" t="inlineStr"/>
-      <c r="DF10" t="inlineStr"/>
-      <c r="DG10" t="inlineStr"/>
-      <c r="DH10" t="inlineStr"/>
-      <c r="DI10" t="inlineStr"/>
-      <c r="DJ10" t="inlineStr"/>
-      <c r="DK10" t="inlineStr"/>
-      <c r="DL10" t="inlineStr"/>
-      <c r="DM10" t="inlineStr"/>
-      <c r="DN10" t="inlineStr"/>
-      <c r="DO10" t="inlineStr"/>
-      <c r="DP10" t="inlineStr"/>
-      <c r="DQ10" t="inlineStr"/>
-      <c r="DR10" t="inlineStr"/>
-      <c r="DS10" t="inlineStr"/>
-      <c r="DT10" t="inlineStr"/>
-      <c r="DU10" t="inlineStr"/>
-      <c r="DV10" t="inlineStr"/>
-      <c r="DW10" t="inlineStr"/>
-      <c r="DX10" t="inlineStr"/>
-      <c r="DY10" t="inlineStr"/>
-      <c r="DZ10" t="inlineStr"/>
-      <c r="EA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4454,139 +4910,139 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="H11" t="n">
+        <v>109.75</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M11" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O11" t="n">
         <v>2</v>
       </c>
-      <c r="C11" t="n">
+      <c r="P11" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>55.25</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1</v>
       </c>
-      <c r="D11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="H11" t="n">
-        <v>106</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="n">
-        <v>6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="M11" t="n">
-        <v>75</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="P11" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>13</v>
-      </c>
-      <c r="R11" t="n">
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
         <v>3</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="AH11" t="n">
         <v>3</v>
       </c>
-      <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>51</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2</v>
-      </c>
       <c r="AI11" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL11" t="n">
-        <v>2</v>
+        <v>4.33</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>30</v>
+        <v>52.33</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ11" t="n">
-        <v>17</v>
+        <v>14.67</v>
       </c>
       <c r="AR11" t="n">
-        <v>1</v>
+        <v>2.67</v>
       </c>
       <c r="AS11" t="n">
-        <v>16</v>
+        <v>11.33</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AU11" t="n">
         <v>0</v>
@@ -4601,73 +5057,73 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48</v>
+        <v>46.33</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>0.33</v>
       </c>
       <c r="BA11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB11" t="n">
-        <v>4</v>
+        <v>4.67</v>
       </c>
       <c r="BC11" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="BD11" t="n">
-        <v>14</v>
+        <v>19.67</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.88</v>
+        <v>1.12</v>
       </c>
       <c r="BF11" t="n">
-        <v>2</v>
+        <v>3.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="BH11" t="n">
-        <v>8.5</v>
+        <v>10.29</v>
       </c>
       <c r="BI11" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="BJ11" t="n">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="BK11" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
-        <v>2</v>
+        <v>1.14</v>
       </c>
       <c r="BM11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BN11" t="n">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>2.5</v>
+        <v>4.14</v>
       </c>
       <c r="BQ11" t="n">
-        <v>1</v>
+        <v>4.57</v>
       </c>
       <c r="BR11" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>100</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>100</v>
+        <v>42.86</v>
       </c>
       <c r="BU11" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -4676,164 +5132,168 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0</v>
+        <v>42.86</v>
       </c>
       <c r="BY11" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="CB11" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="CC11" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="CD11" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="CE11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CF11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CG11" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="CH11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CI11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CJ11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="CK11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CL11" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CM11" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CN11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CO11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="CP11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CQ11" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CR11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CS11" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DA11" t="n">
         <v>1.67</v>
       </c>
-      <c r="BZ11" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="CB11" t="n">
-        <v>4.26</v>
-      </c>
-      <c r="CC11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="CD11" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="CE11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="CF11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="CG11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="CH11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="CI11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CJ11" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="CK11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="CL11" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CM11" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="CN11" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CO11" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="CP11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="CQ11" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CR11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CS11" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="CT11" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="CV11" t="inlineStr"/>
-      <c r="CW11" t="inlineStr"/>
-      <c r="CX11" t="inlineStr"/>
-      <c r="CY11" t="inlineStr"/>
-      <c r="CZ11" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DA11" t="n">
+      <c r="DB11" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="DC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DD11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>97.43000000000001</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>60.57</v>
+      </c>
+      <c r="DL11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DM11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="DN11" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>8</v>
+      </c>
+      <c r="DQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="DW11" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="DX11" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="DY11" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="DZ11" t="n">
         <v>1.62</v>
       </c>
-      <c r="DB11" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="DC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DE11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>88</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>1</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>4</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="DK11" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="DL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM11" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="DN11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="DO11" t="n">
-        <v>7</v>
-      </c>
-      <c r="DP11" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="DQ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT11" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>9</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>5</v>
-      </c>
-      <c r="DX11" t="n">
-        <v>4</v>
-      </c>
-      <c r="DY11" t="n">
-        <v>13</v>
-      </c>
-      <c r="DZ11" t="n">
-        <v>1.24</v>
-      </c>
       <c r="EA11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -4843,139 +5303,139 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>7</v>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="G12" t="n">
         <v>2</v>
       </c>
-      <c r="C12" t="n">
+      <c r="H12" t="n">
+        <v>82.75</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M12" t="n">
+        <v>47.25</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="P12" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R12" t="n">
+        <v>12</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>45.25</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1</v>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="n">
-        <v>85</v>
-      </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>49</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>16</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>17</v>
-      </c>
-      <c r="R12" t="n">
-        <v>10</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" t="n">
-        <v>40</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>14</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>16</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>0</v>
-      </c>
       <c r="AH12" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>96</v>
+        <v>95.67</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>10</v>
+        <v>5.33</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="AO12" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>4.33</v>
       </c>
       <c r="AQ12" t="n">
-        <v>12</v>
+        <v>10.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>3</v>
+        <v>3.33</v>
       </c>
       <c r="AS12" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
@@ -4990,73 +5450,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>17</v>
+        <v>11.67</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>7.67</v>
       </c>
       <c r="BC12" t="n">
         <v>4</v>
       </c>
       <c r="BD12" t="n">
-        <v>23</v>
+        <v>27.67</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.84</v>
+        <v>1.43</v>
       </c>
       <c r="BF12" t="n">
-        <v>2</v>
+        <v>2.67</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.5</v>
+        <v>10.57</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="BK12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5</v>
+        <v>0.86</v>
       </c>
       <c r="BM12" t="n">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="BP12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BQ12" t="n">
-        <v>2.5</v>
+        <v>4.71</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>100</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>28.57</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5065,139 +5525,139 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>100</v>
+        <v>57.14</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.15</v>
+        <v>3.49</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.19</v>
+        <v>3.47</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="CB12" t="n">
         <v>3.79</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.6</v>
+        <v>3.94</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.15</v>
+        <v>4.45</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.17</v>
+        <v>3.12</v>
       </c>
       <c r="CH12" t="n">
         <v>1.48</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.52</v>
+        <v>1.42</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="CN12" t="n">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="CO12" t="n">
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.58</v>
+        <v>2.7</v>
       </c>
       <c r="CR12" t="n">
         <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="CT12" t="n">
         <v>3.19</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="CV12" t="n">
         <v>1.5</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="CX12" t="n">
         <v>2.46</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.94</v>
+        <v>2.08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DB12" t="n">
-        <v>2.84</v>
+        <v>2.76</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="DE12" t="n">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="DF12" t="n">
-        <v>90.5</v>
+        <v>88.29000000000001</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="DH12" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="DI12" t="n">
-        <v>7.5</v>
+        <v>5.57</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="DK12" t="n">
-        <v>58.5</v>
+        <v>51.43</v>
       </c>
       <c r="DL12" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="DM12" t="n">
-        <v>6.5</v>
+        <v>4</v>
       </c>
       <c r="DN12" t="n">
-        <v>14</v>
+        <v>12.14</v>
       </c>
       <c r="DO12" t="n">
-        <v>10</v>
+        <v>4.14</v>
       </c>
       <c r="DP12" t="n">
-        <v>6.5</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
@@ -5209,28 +5669,28 @@
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>45.5</v>
+        <v>47.29</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>15.5</v>
+        <v>10.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>10.5</v>
+        <v>6.57</v>
       </c>
       <c r="DX12" t="n">
-        <v>5</v>
+        <v>4.29</v>
       </c>
       <c r="DY12" t="n">
-        <v>19.5</v>
+        <v>23.43</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="EA12" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="13">
@@ -5240,390 +5700,394 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>7</v>
+      </c>
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H13" t="n">
+        <v>106.33</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.33</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M13" t="n">
+        <v>51.33</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="P13" t="n">
+        <v>13.33</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>12.67</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
         <v>2</v>
       </c>
-      <c r="C13" t="n">
+      <c r="AH13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>92.5</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>40.75</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>27.25</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1</v>
       </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" t="n">
-        <v>2</v>
-      </c>
-      <c r="H13" t="n">
-        <v>124</v>
-      </c>
-      <c r="I13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" t="n">
-        <v>60</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2</v>
-      </c>
-      <c r="P13" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>10</v>
-      </c>
-      <c r="R13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>54</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>17</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>88</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>29</v>
-      </c>
-      <c r="AO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>15</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>33</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE13" t="n">
+      <c r="BP13" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>71.43000000000001</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>14.29</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>42.86</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="CB13" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="CC13" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="CD13" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="CE13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="CF13" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="CG13" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="CH13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="CI13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CJ13" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CK13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CL13" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="CM13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="CN13" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="CO13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="CP13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="CQ13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="CR13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS13" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="CT13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="CU13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CV13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="CW13" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="CX13" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="CY13" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="CZ13" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DA13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="DC13" t="n">
         <v>0.29</v>
       </c>
-      <c r="BF13" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BQ13" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY13" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="BZ13" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="CA13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="CB13" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="CC13" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="CD13" t="n">
-        <v>7.56</v>
-      </c>
-      <c r="CE13" t="n">
+      <c r="DD13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="DE13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="DF13" t="n">
+        <v>98.43000000000001</v>
+      </c>
+      <c r="DG13" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="DH13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="DI13" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="DJ13" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DK13" t="n">
+        <v>47.28</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>13.57</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>42.43</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>26.14</v>
+      </c>
+      <c r="DZ13" t="n">
         <v>1.3</v>
       </c>
-      <c r="CF13" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CG13" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CH13" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="CI13" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="CJ13" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="CK13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="CL13" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="CM13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="CN13" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="CO13" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CP13" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CQ13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="CR13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CS13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="CT13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="CU13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="CV13" t="inlineStr"/>
-      <c r="CW13" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="CX13" t="inlineStr"/>
-      <c r="CY13" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CZ13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="DA13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DB13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DE13" t="n">
-        <v>2</v>
-      </c>
-      <c r="DF13" t="n">
-        <v>106</v>
-      </c>
-      <c r="DG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DI13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="DJ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DK13" t="n">
-        <v>44.5</v>
-      </c>
-      <c r="DL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>13</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>7</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>43.5</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>4</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>3</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>1</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>22</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>0.66</v>
-      </c>
       <c r="EA13" t="n">
-        <v>0.5</v>
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
@@ -1353,13 +1353,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0.25</v>
@@ -1446,49 +1446,49 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AI2" t="n">
-        <v>69</v>
+        <v>73.75</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="AL2" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>32.67</v>
+        <v>39</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>15.33</v>
+        <v>16.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -1500,82 +1500,82 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>40</v>
+        <v>40.75</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.67</v>
+        <v>7.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="BD2" t="n">
-        <v>19</v>
+        <v>18.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.91</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.14</v>
+        <v>10</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL2" t="n">
         <v>1</v>
       </c>
       <c r="BM2" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="BN2" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="BO2" t="n">
         <v>1</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.71</v>
+        <v>4.25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.43</v>
+        <v>5.75</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU2" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BV2" t="n">
-        <v>28.57</v>
+        <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY2" t="n">
         <v>3.51</v>
@@ -1584,16 +1584,16 @@
         <v>3.68</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.09</v>
+        <v>4.05</v>
       </c>
       <c r="CC2" t="n">
-        <v>4.52</v>
+        <v>4.24</v>
       </c>
       <c r="CD2" t="n">
-        <v>4.72</v>
+        <v>4.37</v>
       </c>
       <c r="CE2" t="n">
         <v>1.29</v>
@@ -1602,25 +1602,25 @@
         <v>2.44</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.59</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CL2" t="n">
         <v>1.68</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CN2" t="n">
         <v>2.27</v>
@@ -1632,7 +1632,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="CX2" t="inlineStr"/>
       <c r="CY2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CZ2" t="n">
         <v>1.19</v>
@@ -1664,46 +1664,46 @@
         <v>2.53</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="DE2" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="DF2" t="n">
-        <v>80.86</v>
+        <v>81.75</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="DI2" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DK2" t="n">
-        <v>34.86</v>
+        <v>37.75</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="DN2" t="n">
-        <v>11.86</v>
+        <v>12.75</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.71</v>
+        <v>7.75</v>
       </c>
       <c r="DQ2" t="n">
         <v>0</v>
@@ -1715,28 +1715,28 @@
         <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>41.86</v>
+        <v>42</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DV2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DW2" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="DY2" t="n">
-        <v>20.14</v>
+        <v>19.88</v>
       </c>
       <c r="DZ2" t="n">
         <v>1.04</v>
       </c>
       <c r="EA2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -1746,13 +1746,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" t="n">
         <v>4</v>
       </c>
       <c r="D3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1836,16 +1836,16 @@
         <v>1.25</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>90.25</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1854,112 +1854,112 @@
         <v>1</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AN3" t="n">
-        <v>54.5</v>
+        <v>49.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AP3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC3" t="n">
         <v>3</v>
       </c>
-      <c r="AQ3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>50.5</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>3.25</v>
-      </c>
       <c r="BD3" t="n">
-        <v>24.75</v>
+        <v>23.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
         <v>1</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.88</v>
+        <v>10.67</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BN3" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="BP3" t="n">
         <v>6</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>62.5</v>
+        <v>66.67</v>
       </c>
       <c r="BT3" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU3" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY3" t="n">
         <v>1.57</v>
@@ -1977,31 +1977,31 @@
         <v>1.62</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.97</v>
+        <v>3.9</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.13</v>
+        <v>4.08</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="CD3" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.37</v>
+        <v>2.39</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.59</v>
@@ -2013,19 +2013,19 @@
         <v>1.64</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CO3" t="n">
         <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2041,62 +2041,62 @@
       </c>
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="DE3" t="n">
         <v>2</v>
       </c>
       <c r="DF3" t="n">
-        <v>98.88</v>
+        <v>96.33</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DI3" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DK3" t="n">
-        <v>58.25</v>
+        <v>55</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="DN3" t="n">
-        <v>10.25</v>
+        <v>10.56</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.25</v>
+        <v>5.44</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
@@ -2108,28 +2108,28 @@
         <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DV3" t="n">
-        <v>12.25</v>
+        <v>12.33</v>
       </c>
       <c r="DW3" t="n">
-        <v>8.25</v>
+        <v>8.56</v>
       </c>
       <c r="DX3" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="DY3" t="n">
-        <v>22.62</v>
+        <v>22.33</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="4">
@@ -2139,10 +2139,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
         <v>5</v>
@@ -2151,64 +2151,64 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.33</v>
+        <v>1.25</v>
       </c>
       <c r="G4" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="H4" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="K4" t="n">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>52.33</v>
+        <v>51</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>11.67</v>
+        <v>11.5</v>
       </c>
       <c r="Q4" t="n">
+        <v>5</v>
+      </c>
+      <c r="R4" t="n">
         <v>9</v>
       </c>
-      <c r="R4" t="n">
-        <v>8.33</v>
-      </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>46.33</v>
+        <v>48.75</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z4" t="n">
         <v>8</v>
@@ -2220,13 +2220,13 @@
         <v>3</v>
       </c>
       <c r="AC4" t="n">
-        <v>20</v>
+        <v>20.25</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AF4" t="n">
         <v>0.2</v>
@@ -2310,70 +2310,70 @@
         <v>1.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.619999999999999</v>
+        <v>9.67</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.12</v>
+        <v>3.78</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.5</v>
+        <v>5.78</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT4" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BU4" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BV4" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>87.5</v>
+        <v>77.78</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
       <c r="BZ4" t="n">
-        <v>2.82</v>
+        <v>2.65</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC4" t="n">
         <v>2.76</v>
@@ -2385,31 +2385,31 @@
         <v>1.32</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH4" t="n">
         <v>1.5</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO4" t="n">
         <v>1.2</v>
@@ -2418,7 +2418,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CR4" t="n">
         <v>1.34</v>
@@ -2450,79 +2450,79 @@
         <v>2.72</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.62</v>
+        <v>1</v>
       </c>
       <c r="DE4" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="DF4" t="n">
-        <v>87</v>
+        <v>86.89</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DH4" t="n">
-        <v>1.37</v>
+        <v>1.78</v>
       </c>
       <c r="DI4" t="n">
-        <v>3.37</v>
+        <v>3.56</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DK4" t="n">
-        <v>43.75</v>
+        <v>44.11</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DN4" t="n">
-        <v>9.880000000000001</v>
+        <v>10</v>
       </c>
       <c r="DO4" t="n">
-        <v>4.5</v>
+        <v>3.22</v>
       </c>
       <c r="DP4" t="n">
-        <v>9</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="DU4" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DV4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DW4" t="n">
-        <v>6</v>
+        <v>5.89</v>
       </c>
       <c r="DX4" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="DY4" t="n">
-        <v>16.75</v>
+        <v>17.22</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="EA4" t="n">
-        <v>1.37</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="5">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -2544,49 +2544,49 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>3.67</v>
       </c>
       <c r="H5" t="n">
-        <v>91.8</v>
+        <v>99.5</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="K5" t="n">
-        <v>7.2</v>
+        <v>6.83</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="M5" t="n">
-        <v>65.8</v>
+        <v>67.83</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
-        <v>3</v>
+        <v>3.17</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R5" t="n">
-        <v>4.2</v>
+        <v>5.33</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -2598,28 +2598,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>61</v>
+        <v>60.5</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>15.2</v>
+        <v>15.33</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.6</v>
+        <v>9.67</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.6</v>
+        <v>5.67</v>
       </c>
       <c r="AC5" t="n">
-        <v>20</v>
+        <v>20.17</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.6</v>
+        <v>1.83</v>
       </c>
       <c r="AF5" t="n">
         <v>0.75</v>
@@ -2640,7 +2640,7 @@
         <v>1.25</v>
       </c>
       <c r="AL5" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AM5" t="n">
         <v>0.75</v>
@@ -2658,7 +2658,7 @@
         <v>10.5</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.75</v>
+        <v>2.25</v>
       </c>
       <c r="AS5" t="n">
         <v>9.25</v>
@@ -2679,73 +2679,73 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>52.75</v>
+        <v>53</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="BB5" t="n">
         <v>5.25</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.75</v>
+        <v>20.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BF5" t="n">
         <v>1.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.33</v>
+        <v>10</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BN5" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="BR5" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS5" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT5" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU5" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.78</v>
+        <v>3.82</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="CC5" t="n">
         <v>1.92</v>
@@ -2775,52 +2775,52 @@
         <v>2</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF5" t="n">
         <v>2.54</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH5" t="n">
         <v>1.44</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="CJ5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="CL5" t="n">
         <v>1.74</v>
       </c>
-      <c r="CK5" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="CL5" t="n">
-        <v>1.75</v>
-      </c>
       <c r="CM5" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="CQ5" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.14</v>
+        <v>3.16</v>
       </c>
       <c r="CU5" t="n">
         <v>1.47</v>
@@ -2847,79 +2847,79 @@
         <v>3.09</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DE5" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="DF5" t="n">
-        <v>89.44</v>
+        <v>94.3</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="DI5" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="DJ5" t="n">
         <v>1</v>
       </c>
       <c r="DK5" t="n">
-        <v>59.11</v>
+        <v>61</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="DN5" t="n">
-        <v>10.22</v>
+        <v>10.8</v>
       </c>
       <c r="DO5" t="n">
-        <v>3.11</v>
+        <v>2</v>
       </c>
       <c r="DP5" t="n">
-        <v>6.44</v>
+        <v>6.9</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>57.33</v>
+        <v>57.5</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>12.67</v>
+        <v>13.1</v>
       </c>
       <c r="DW5" t="n">
-        <v>7.67</v>
+        <v>7.9</v>
       </c>
       <c r="DX5" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="DY5" t="n">
-        <v>20.33</v>
+        <v>20.2</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -2929,94 +2929,94 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="H6" t="n">
-        <v>97</v>
+        <v>95.5</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>62</v>
+        <v>64.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
       </c>
       <c r="P6" t="n">
-        <v>14.67</v>
+        <v>15.75</v>
       </c>
       <c r="Q6" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AB6" t="n">
         <v>5</v>
       </c>
-      <c r="R6" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>49</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>3.67</v>
-      </c>
       <c r="AC6" t="n">
-        <v>23.33</v>
+        <v>24.25</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.28</v>
+        <v>1.48</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF6" t="n">
         <v>0.2</v>
@@ -3055,10 +3055,10 @@
         <v>10.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.8</v>
+        <v>1.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT6" t="n">
         <v>2.2</v>
@@ -3076,16 +3076,16 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.2</v>
+        <v>45.8</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.2</v>
+        <v>11.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
         <v>4</v>
@@ -3094,76 +3094,76 @@
         <v>16.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BF6" t="n">
         <v>1</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BH6" t="n">
-        <v>7.88</v>
+        <v>7.67</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL6" t="n">
         <v>1</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="BQ6" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BR6" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS6" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT6" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.23</v>
+        <v>2.88</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.51</v>
+        <v>3.1</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="CC6" t="n">
         <v>4.21</v>
@@ -3172,43 +3172,43 @@
         <v>4.65</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CK6" t="n">
         <v>1.4</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN6" t="n">
         <v>2.07</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3234,85 +3234,85 @@
         <v>1.24</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DB6" t="n">
-        <v>2.85</v>
+        <v>2.92</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DD6" t="n">
         <v>1</v>
       </c>
       <c r="DE6" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="DF6" t="n">
-        <v>95.75</v>
+        <v>95.22</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="DI6" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DK6" t="n">
-        <v>52.75</v>
+        <v>54.89</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DM6" t="n">
         <v>1</v>
       </c>
       <c r="DN6" t="n">
-        <v>12.13</v>
+        <v>12.89</v>
       </c>
       <c r="DO6" t="n">
-        <v>4.25</v>
+        <v>2.89</v>
       </c>
       <c r="DP6" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>46.62</v>
+        <v>46.56</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>11</v>
+        <v>11.22</v>
       </c>
       <c r="DW6" t="n">
-        <v>7.12</v>
+        <v>6.78</v>
       </c>
       <c r="DX6" t="n">
-        <v>3.88</v>
+        <v>4.44</v>
       </c>
       <c r="DY6" t="n">
-        <v>19.12</v>
+        <v>20</v>
       </c>
       <c r="DZ6" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="EA6" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="7">
@@ -3322,94 +3322,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.17</v>
       </c>
       <c r="H7" t="n">
-        <v>116.4</v>
+        <v>110.33</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4</v>
+        <v>-0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="K7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
-        <v>66.8</v>
+        <v>66.33</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>5.17</v>
       </c>
       <c r="P7" t="n">
-        <v>10.6</v>
+        <v>11</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.4</v>
+        <v>2.17</v>
       </c>
       <c r="R7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6</v>
+        <v>0.67</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>61</v>
+        <v>58.5</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>17</v>
+        <v>17.17</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.6</v>
+        <v>11.33</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.4</v>
+        <v>5.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>16.8</v>
+        <v>18.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3493,70 +3493,70 @@
         <v>1.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.22</v>
+        <v>11.2</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BP7" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.89</v>
+        <v>4.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT7" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU7" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV7" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="CC7" t="n">
         <v>2.03</v>
@@ -3565,43 +3565,43 @@
         <v>2.28</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.11</v>
+        <v>2.07</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="CK7" t="n">
         <v>1.43</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="CR7" t="n">
         <v>1.36</v>
@@ -3616,100 +3616,100 @@
         <v>1.54</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CX7" t="n">
-        <v>2.41</v>
+        <v>2.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CZ7" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DE7" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>121.67</v>
+        <v>117.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.22</v>
+        <v>-0.2</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="DI7" t="n">
-        <v>7.56</v>
+        <v>7.7</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="DK7" t="n">
-        <v>68.67</v>
+        <v>68.2</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>4.44</v>
+        <v>4.6</v>
       </c>
       <c r="DN7" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.11</v>
+        <v>2.4</v>
       </c>
       <c r="DP7" t="n">
-        <v>8.220000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DR7" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>61.89</v>
+        <v>60.3</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DV7" t="n">
-        <v>15.11</v>
+        <v>15.4</v>
       </c>
       <c r="DW7" t="n">
-        <v>9.220000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>5.89</v>
+        <v>5.6</v>
       </c>
       <c r="DY7" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="8">
@@ -3719,13 +3719,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>0.25</v>
@@ -3809,127 +3809,127 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AG8" t="n">
-        <v>3.33</v>
+        <v>2.75</v>
       </c>
       <c r="AH8" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>76.67</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="AL8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AS8" t="n">
         <v>6</v>
       </c>
-      <c r="AM8" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>42.67</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>3.67</v>
-      </c>
       <c r="AT8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>20.75</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="BJ8" t="n">
         <v>1</v>
       </c>
-      <c r="AU8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>11.67</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.86</v>
-      </c>
       <c r="BK8" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>4.38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT8" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY8" t="n">
         <v>2.62</v>
@@ -3950,43 +3950,43 @@
         <v>2.68</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.52</v>
+        <v>3.57</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.45</v>
+        <v>4.24</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CG8" t="n">
         <v>2.86</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="CK8" t="n">
         <v>1.46</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CN8" t="n">
         <v>1.97</v>
@@ -3995,10 +3995,10 @@
         <v>1.27</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
@@ -4013,13 +4013,13 @@
         <v>1.41</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CX8" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="CY8" t="n">
         <v>1.99</v>
@@ -4028,52 +4028,52 @@
         <v>1.3</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="DB8" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.28</v>
+        <v>2.12</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="DF8" t="n">
-        <v>89.72</v>
+        <v>87.25</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="DI8" t="n">
-        <v>5.29</v>
+        <v>4.88</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="DK8" t="n">
-        <v>45.29</v>
+        <v>42.88</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.57</v>
+        <v>0.88</v>
       </c>
       <c r="DM8" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DN8" t="n">
-        <v>12.86</v>
+        <v>12.75</v>
       </c>
       <c r="DO8" t="n">
-        <v>4.71</v>
+        <v>4.25</v>
       </c>
       <c r="DP8" t="n">
-        <v>6</v>
+        <v>6.88</v>
       </c>
       <c r="DQ8" t="n">
         <v>0</v>
@@ -4085,28 +4085,28 @@
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>54.14</v>
+        <v>53.75</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DV8" t="n">
-        <v>11.14</v>
+        <v>10.88</v>
       </c>
       <c r="DW8" t="n">
-        <v>7.71</v>
+        <v>7.38</v>
       </c>
       <c r="DX8" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>23.14</v>
+        <v>22.88</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="9">
@@ -4116,13 +4116,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4212,16 +4212,16 @@
         <v>1</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>87</v>
+        <v>91.25</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AL9" t="n">
         <v>4</v>
@@ -4230,106 +4230,106 @@
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>34.67</v>
+        <v>41.25</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.67</v>
+        <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AS9" t="n">
-        <v>12.33</v>
+        <v>10.25</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>44.33</v>
+        <v>47.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="BB9" t="n">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="BC9" t="n">
         <v>1</v>
       </c>
       <c r="BD9" t="n">
-        <v>19.67</v>
+        <v>19</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.52</v>
+        <v>0.62</v>
       </c>
       <c r="BF9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BH9" t="n">
-        <v>11.14</v>
+        <v>10.5</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN9" t="n">
         <v>1</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="BP9" t="n">
-        <v>5.14</v>
+        <v>4.88</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT9" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU9" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.14</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>4.01</v>
@@ -4347,31 +4347,31 @@
         <v>4.67</v>
       </c>
       <c r="CA9" t="n">
-        <v>4.01</v>
+        <v>3.93</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="CC9" t="n">
-        <v>6.17</v>
+        <v>5.58</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.94</v>
+        <v>7.02</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.43</v>
+        <v>2.49</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.74</v>
@@ -4380,22 +4380,22 @@
         <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN9" t="n">
         <v>2.09</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.66</v>
+        <v>2.73</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4422,88 +4422,88 @@
         <v>2.06</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.86</v>
+        <v>2.94</v>
       </c>
       <c r="DC9" t="n">
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="DE9" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="DF9" t="n">
-        <v>82.70999999999999</v>
+        <v>85.38</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DH9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="DI9" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DK9" t="n">
-        <v>34.72</v>
+        <v>38</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DM9" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DN9" t="n">
-        <v>11.57</v>
+        <v>11.38</v>
       </c>
       <c r="DO9" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.14</v>
+        <v>10.25</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
       </c>
       <c r="DT9" t="n">
-        <v>46.14</v>
+        <v>47.5</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>5.71</v>
+        <v>5.75</v>
       </c>
       <c r="DW9" t="n">
-        <v>3.43</v>
+        <v>3.62</v>
       </c>
       <c r="DX9" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DY9" t="n">
-        <v>21.57</v>
+        <v>21</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="EA9" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="10">
@@ -4513,13 +4513,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
         <v>3</v>
       </c>
       <c r="D10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E10" t="n">
         <v>0.33</v>
@@ -4606,136 +4606,136 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.8</v>
+        <v>0.83</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>84.8</v>
+        <v>78</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.2</v>
+        <v>-0.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AL10" t="n">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AN10" t="n">
-        <v>43.6</v>
+        <v>38.17</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>10.8</v>
+        <v>10.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.8</v>
+        <v>4.33</v>
       </c>
       <c r="AS10" t="n">
-        <v>7.2</v>
+        <v>9.17</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.4</v>
+        <v>1.17</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>48.4</v>
+        <v>45.5</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.4</v>
+        <v>11.5</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
         <v>4</v>
       </c>
       <c r="BD10" t="n">
-        <v>22.2</v>
+        <v>21.33</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="BF10" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.88</v>
+        <v>4.78</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.38</v>
+        <v>4.33</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BT10" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU10" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BV10" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BW10" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX10" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BY10" t="n">
         <v>2.08</v>
@@ -4744,34 +4744,34 @@
         <v>2.11</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.66</v>
+        <v>3.63</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC10" t="n">
-        <v>3.02</v>
+        <v>2.92</v>
       </c>
       <c r="CD10" t="n">
-        <v>3.17</v>
+        <v>3.1</v>
       </c>
       <c r="CE10" t="n">
         <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK10" t="n">
         <v>1.41</v>
@@ -4780,7 +4780,7 @@
         <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CN10" t="n">
         <v>2.03</v>
@@ -4798,10 +4798,10 @@
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CU10" t="n">
         <v>1.51</v>
@@ -4828,79 +4828,79 @@
         <v>2.94</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DD10" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="DE10" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="DF10" t="n">
-        <v>84.12</v>
+        <v>79.67</v>
       </c>
       <c r="DG10" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DH10" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="DI10" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DK10" t="n">
-        <v>44</v>
+        <v>40.34</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM10" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="DN10" t="n">
-        <v>11.37</v>
+        <v>11.22</v>
       </c>
       <c r="DO10" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="DP10" t="n">
-        <v>7.88</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DS10" t="n">
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>46.87</v>
+        <v>45.11</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DV10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="DW10" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="DX10" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="DY10" t="n">
-        <v>24.5</v>
+        <v>23.66</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="EA10" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="11">
@@ -4910,10 +4910,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
@@ -4922,13 +4922,13 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>109.75</v>
+        <v>116.8</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -4940,31 +4940,31 @@
         <v>7</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>66.75</v>
+        <v>68.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="P11" t="n">
-        <v>12.75</v>
+        <v>12.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="S11" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -4976,25 +4976,25 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>55.25</v>
+        <v>58</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>17.75</v>
+        <v>17.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.75</v>
+        <v>5.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AE11" t="n">
         <v>1</v>
@@ -5081,49 +5081,49 @@
         <v>3.33</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.29</v>
+        <v>10</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="BL11" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="BO11" t="n">
         <v>1</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>85.70999999999999</v>
+        <v>75</v>
       </c>
       <c r="BT11" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV11" t="n">
         <v>0</v>
@@ -5132,19 +5132,19 @@
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>42.86</v>
+        <v>37.5</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.7</v>
+        <v>3.67</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.95</v>
+        <v>3.92</v>
       </c>
       <c r="CC11" t="n">
         <v>3.55</v>
@@ -5156,40 +5156,40 @@
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI11" t="n">
         <v>2.26</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK11" t="n">
         <v>1.37</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO11" t="n">
         <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5201,15 +5201,15 @@
         <v>3.3</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CZ11" t="n">
         <v>1.21</v>
@@ -5224,43 +5224,43 @@
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="DF11" t="n">
-        <v>97.43000000000001</v>
+        <v>103.38</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="DI11" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DK11" t="n">
-        <v>60.57</v>
+        <v>62.62</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DM11" t="n">
-        <v>1.71</v>
+        <v>1.87</v>
       </c>
       <c r="DN11" t="n">
-        <v>13.57</v>
+        <v>13.5</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.72</v>
+        <v>3.13</v>
       </c>
       <c r="DP11" t="n">
-        <v>8</v>
+        <v>7.37</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
@@ -5272,28 +5272,28 @@
         <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>51.43</v>
+        <v>53.62</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DV11" t="n">
-        <v>13.57</v>
+        <v>13.75</v>
       </c>
       <c r="DW11" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="DX11" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="DY11" t="n">
-        <v>19.29</v>
+        <v>19.88</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="EA11" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="12">
@@ -5303,13 +5303,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" t="n">
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5396,46 +5396,46 @@
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AI12" t="n">
-        <v>95.67</v>
+        <v>97.75</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>5.33</v>
+        <v>4.25</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP12" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10.33</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>3.33</v>
+        <v>3.75</v>
       </c>
       <c r="AS12" t="n">
-        <v>4.33</v>
+        <v>6.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
@@ -5450,73 +5450,73 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.67</v>
+        <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>27.67</v>
+        <v>26.5</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.57</v>
+        <v>10</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="BP12" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>28.57</v>
+        <v>37.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.14</v>
+        <v>62.5</v>
       </c>
       <c r="BY12" t="n">
         <v>3.49</v>
@@ -5534,16 +5534,16 @@
         <v>3.47</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.56</v>
+        <v>3.64</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.94</v>
+        <v>4.52</v>
       </c>
       <c r="CD12" t="n">
-        <v>4.45</v>
+        <v>4.86</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
@@ -5552,49 +5552,49 @@
         <v>2.54</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.15</v>
+        <v>2.11</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="CK12" t="n">
         <v>1.42</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CO12" t="n">
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV12" t="n">
         <v>1.5</v>
@@ -5609,88 +5609,88 @@
         <v>2.08</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DB12" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="DF12" t="n">
-        <v>88.29000000000001</v>
+        <v>90.25</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DH12" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DI12" t="n">
-        <v>5.57</v>
+        <v>5</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DK12" t="n">
-        <v>51.43</v>
+        <v>52.62</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="DM12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="DN12" t="n">
+        <v>12.25</v>
+      </c>
+      <c r="DO12" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="DP12" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="DQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT12" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="DU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV12" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="DW12" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="DX12" t="n">
         <v>4</v>
       </c>
-      <c r="DN12" t="n">
-        <v>12.14</v>
-      </c>
-      <c r="DO12" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="DP12" t="n">
-        <v>8.710000000000001</v>
-      </c>
-      <c r="DQ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT12" t="n">
-        <v>47.29</v>
-      </c>
-      <c r="DU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV12" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="DW12" t="n">
-        <v>6.57</v>
-      </c>
-      <c r="DX12" t="n">
-        <v>4.29</v>
-      </c>
       <c r="DY12" t="n">
-        <v>23.43</v>
+        <v>23.38</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EA12" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -5700,94 +5700,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.67</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>106.33</v>
+        <v>107.5</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="K13" t="n">
-        <v>7.33</v>
+        <v>6.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="M13" t="n">
-        <v>51.33</v>
+        <v>49.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>3.67</v>
+        <v>3.75</v>
       </c>
       <c r="P13" t="n">
-        <v>13.33</v>
+        <v>15.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.67</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>9</v>
+        <v>8.25</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="V13" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44.67</v>
+        <v>44.25</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>12.67</v>
+        <v>12.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.33</v>
+        <v>8.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>24.67</v>
+        <v>24.25</v>
       </c>
       <c r="AD13" t="n">
         <v>1.48</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.33</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5871,70 +5871,70 @@
         <v>1.25</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.43</v>
+        <v>10.25</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="BO13" t="n">
         <v>1</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.86</v>
+        <v>5.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>71.43000000000001</v>
+        <v>75</v>
       </c>
       <c r="BS13" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BT13" t="n">
-        <v>14.29</v>
+        <v>25</v>
       </c>
       <c r="BU13" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>14.29</v>
+        <v>12.5</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>42.86</v>
+        <v>50</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="CC13" t="n">
         <v>4.43</v>
@@ -5946,40 +5946,40 @@
         <v>1.35</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CG13" t="n">
         <v>2.99</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CO13" t="n">
         <v>1.24</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CR13" t="n">
         <v>1.38</v>
@@ -5997,97 +5997,97 @@
         <v>1.48</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="CX13" t="n">
         <v>2.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="CZ13" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DA13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="DB13" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="DC13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DD13" t="n">
         <v>1.88</v>
       </c>
-      <c r="DB13" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="DC13" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="DD13" t="n">
-        <v>1.57</v>
-      </c>
       <c r="DE13" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="DF13" t="n">
-        <v>98.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="DH13" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="DI13" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="DK13" t="n">
-        <v>47.28</v>
+        <v>46.88</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DM13" t="n">
-        <v>2.57</v>
+        <v>2.75</v>
       </c>
       <c r="DN13" t="n">
-        <v>13.57</v>
+        <v>14.75</v>
       </c>
       <c r="DO13" t="n">
-        <v>3.29</v>
+        <v>4.5</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.859999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>42.43</v>
+        <v>42.5</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="DV13" t="n">
-        <v>10.57</v>
+        <v>10.88</v>
       </c>
       <c r="DW13" t="n">
-        <v>6.43</v>
+        <v>6.62</v>
       </c>
       <c r="DX13" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="DY13" t="n">
-        <v>26.14</v>
+        <v>25.75</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
@@ -1353,61 +1353,61 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
         <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="G2" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="H2" t="n">
-        <v>89.75</v>
+        <v>82.8</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>36.5</v>
+        <v>35.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="O2" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="P2" t="n">
-        <v>9.25</v>
+        <v>10.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="R2" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>2</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -1419,28 +1419,28 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>43.25</v>
+        <v>41.4</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="AB2" t="n">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="AC2" t="n">
         <v>21</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1479,7 +1479,7 @@
         <v>16.25</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.75</v>
+        <v>4</v>
       </c>
       <c r="AS2" t="n">
         <v>7.5</v>
@@ -1500,16 +1500,16 @@
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>40.75</v>
+        <v>42.25</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.25</v>
       </c>
       <c r="BA2" t="n">
-        <v>7.25</v>
+        <v>7.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.5</v>
+        <v>4.75</v>
       </c>
       <c r="BC2" t="n">
         <v>2.75</v>
@@ -1518,76 +1518,76 @@
         <v>18.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="BF2" t="n">
         <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="BH2" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BL2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.25</v>
+        <v>4.44</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BT2" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU2" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>33.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY2" t="n">
-        <v>3.51</v>
+        <v>3.35</v>
       </c>
       <c r="BZ2" t="n">
-        <v>3.68</v>
+        <v>3.48</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CB2" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="CC2" t="n">
         <v>4.24</v>
@@ -1602,13 +1602,13 @@
         <v>2.44</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH2" t="n">
         <v>1.52</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.59</v>
@@ -1617,22 +1617,22 @@
         <v>1.3</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM2" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CO2" t="n">
         <v>1.18</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1655,55 +1655,55 @@
         <v>2.31</v>
       </c>
       <c r="CZ2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DA2" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DB2" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DD2" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="DE2" t="n">
-        <v>2.38</v>
+        <v>2.22</v>
       </c>
       <c r="DF2" t="n">
-        <v>81.75</v>
+        <v>78.78</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="DI2" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>37.75</v>
+        <v>37.11</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DM2" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="DN2" t="n">
-        <v>12.75</v>
+        <v>12.89</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.5</v>
+        <v>3.67</v>
       </c>
       <c r="DP2" t="n">
-        <v>7.75</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DQ2" t="n">
         <v>0</v>
@@ -1715,28 +1715,28 @@
         <v>0</v>
       </c>
       <c r="DT2" t="n">
-        <v>42</v>
+        <v>41.78</v>
       </c>
       <c r="DU2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DV2" t="n">
-        <v>8.380000000000001</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DW2" t="n">
-        <v>5.12</v>
+        <v>5.44</v>
       </c>
       <c r="DX2" t="n">
-        <v>3.25</v>
+        <v>3.78</v>
       </c>
       <c r="DY2" t="n">
-        <v>19.88</v>
+        <v>20</v>
       </c>
       <c r="DZ2" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="EA2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="3">
@@ -1746,10 +1746,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
         <v>5</v>
@@ -1758,82 +1758,82 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="H3" t="n">
-        <v>107.5</v>
+        <v>105.2</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="M3" t="n">
-        <v>62</v>
+        <v>66.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
-        <v>9.5</v>
+        <v>10.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="R3" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="S3" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>54.5</v>
+        <v>55.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>13.25</v>
+        <v>14.2</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.75</v>
+        <v>4.4</v>
       </c>
       <c r="AC3" t="n">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AF3" t="n">
         <v>0.2</v>
@@ -1893,16 +1893,16 @@
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>51.8</v>
+        <v>52.2</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC3" t="n">
         <v>3</v>
@@ -1911,55 +1911,55 @@
         <v>23.8</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="BF3" t="n">
         <v>1</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>10.67</v>
+        <v>10.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="BP3" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>66.67</v>
+        <v>60</v>
       </c>
       <c r="BT3" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BU3" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BV3" t="n">
         <v>0</v>
@@ -1968,19 +1968,19 @@
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>44.44</v>
+        <v>40</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="CB3" t="n">
-        <v>4.08</v>
+        <v>4.44</v>
       </c>
       <c r="CC3" t="n">
         <v>2.2</v>
@@ -1989,43 +1989,43 @@
         <v>2.31</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.24</v>
+        <v>2.19</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="CK3" t="n">
         <v>1.32</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="CM3" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2041,95 +2041,95 @@
       </c>
       <c r="CV3" t="inlineStr"/>
       <c r="CW3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="CZ3" t="n">
         <v>1.2</v>
       </c>
       <c r="DA3" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="DB3" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DE3" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="DF3" t="n">
-        <v>96.33</v>
+        <v>96.3</v>
       </c>
       <c r="DG3" t="n">
         <v>0</v>
       </c>
       <c r="DH3" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DI3" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>55</v>
+        <v>57.8</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="DM3" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DN3" t="n">
-        <v>10.56</v>
+        <v>10.8</v>
       </c>
       <c r="DO3" t="n">
-        <v>5.44</v>
+        <v>4.9</v>
       </c>
       <c r="DP3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DR3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="DS3" t="n">
         <v>0</v>
       </c>
       <c r="DT3" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DV3" t="n">
-        <v>12.33</v>
+        <v>13</v>
       </c>
       <c r="DW3" t="n">
-        <v>8.56</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DX3" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="DY3" t="n">
-        <v>22.33</v>
+        <v>22</v>
       </c>
       <c r="DZ3" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -2184,7 +2184,7 @@
         <v>11.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>5</v>
+        <v>9.5</v>
       </c>
       <c r="R4" t="n">
         <v>9</v>
@@ -2205,7 +2205,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.75</v>
+        <v>47.25</v>
       </c>
       <c r="Y4" t="n">
         <v>0.25</v>
@@ -2229,139 +2229,139 @@
         <v>1.75</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>78.17</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>36.67</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.67</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BK4" t="n">
         <v>0.8</v>
       </c>
-      <c r="AH4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>78</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>38.6</v>
-      </c>
-      <c r="AO4" t="n">
+      <c r="BL4" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="BM4" t="n">
         <v>0.6</v>
       </c>
-      <c r="AP4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>10.2</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>0.67</v>
-      </c>
       <c r="BN4" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BP4" t="n">
-        <v>3.78</v>
+        <v>3.3</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.78</v>
+        <v>5.1</v>
       </c>
       <c r="BR4" t="n">
         <v>100</v>
       </c>
       <c r="BS4" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BT4" t="n">
-        <v>66.67</v>
+        <v>70</v>
       </c>
       <c r="BU4" t="n">
-        <v>55.56</v>
+        <v>60</v>
       </c>
       <c r="BV4" t="n">
-        <v>11.11</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>77.78</v>
+        <v>70</v>
       </c>
       <c r="BY4" t="n">
         <v>2.53</v>
@@ -2370,159 +2370,163 @@
         <v>2.65</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.56</v>
+        <v>3.54</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.85</v>
+        <v>3.81</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CD4" t="n">
         <v>3.04</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.12</v>
+        <v>3.08</v>
       </c>
       <c r="CH4" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CI4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="CO4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="CP4" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="CQ4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="CU4" t="n">
         <v>1.5</v>
       </c>
-      <c r="CI4" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="CJ4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CK4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CL4" t="n">
+      <c r="CV4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CX4" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="CY4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="DA4" t="n">
         <v>1.76</v>
       </c>
-      <c r="CM4" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CN4" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="CO4" t="n">
+      <c r="DB4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DD4" t="n">
         <v>1.2</v>
       </c>
-      <c r="CP4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="CQ4" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="CR4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="CS4" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CT4" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="CU4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CV4" t="inlineStr"/>
-      <c r="CW4" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CX4" t="inlineStr"/>
-      <c r="CY4" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CZ4" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="DA4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="DB4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="DC4" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DD4" t="n">
-        <v>1</v>
-      </c>
       <c r="DE4" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="DF4" t="n">
-        <v>86.89</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DH4" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="DI4" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="DK4" t="n">
-        <v>44.11</v>
+        <v>42.4</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="DM4" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="DN4" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
       <c r="DO4" t="n">
-        <v>3.22</v>
+        <v>5.4</v>
       </c>
       <c r="DP4" t="n">
-        <v>9.220000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
       </c>
       <c r="DT4" t="n">
-        <v>48</v>
+        <v>47.1</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DV4" t="n">
-        <v>9.220000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="DW4" t="n">
-        <v>5.89</v>
+        <v>5.8</v>
       </c>
       <c r="DX4" t="n">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="DY4" t="n">
-        <v>17.22</v>
+        <v>17.3</v>
       </c>
       <c r="DZ4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="EA4" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5">
@@ -2532,13 +2536,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -2622,130 +2626,130 @@
         <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>86.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="AL5" t="n">
-        <v>6.25</v>
+        <v>5.4</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="AN5" t="n">
-        <v>50.75</v>
+        <v>47.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AQ5" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.25</v>
+        <v>8.6</v>
       </c>
       <c r="AT5" t="n">
         <v>1</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX5" t="n">
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>53</v>
+        <v>53.4</v>
       </c>
       <c r="AZ5" t="n">
         <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.25</v>
+        <v>5.6</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.25</v>
+        <v>20.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="BG5" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BH5" t="n">
-        <v>10</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.7</v>
+        <v>4.55</v>
       </c>
       <c r="BR5" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS5" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU5" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV5" t="n">
         <v>0</v>
@@ -2754,7 +2758,7 @@
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>50</v>
+        <v>54.55</v>
       </c>
       <c r="BY5" t="n">
         <v>1.67</v>
@@ -2763,163 +2767,163 @@
         <v>1.76</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.82</v>
+        <v>3.77</v>
       </c>
       <c r="CB5" t="n">
-        <v>4.08</v>
+        <v>4.02</v>
       </c>
       <c r="CC5" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="CD5" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="CG5" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI5" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.75</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.73</v>
+        <v>2.71</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="CO5" t="n">
         <v>1.24</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.99</v>
+        <v>3.06</v>
       </c>
       <c r="CR5" t="n">
         <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.76</v>
+        <v>2.79</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.16</v>
+        <v>3.12</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CV5" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CX5" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="CY5" t="n">
-        <v>2.12</v>
+        <v>2.09</v>
       </c>
       <c r="CZ5" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DA5" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="DB5" t="n">
-        <v>3.09</v>
+        <v>3.12</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DD5" t="n">
-        <v>1.3</v>
+        <v>1.45</v>
       </c>
       <c r="DE5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="DF5" t="n">
-        <v>94.3</v>
+        <v>92.27</v>
       </c>
       <c r="DG5" t="n">
         <v>0</v>
       </c>
       <c r="DH5" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="DI5" t="n">
-        <v>6.6</v>
+        <v>6.18</v>
       </c>
       <c r="DJ5" t="n">
         <v>1</v>
       </c>
       <c r="DK5" t="n">
-        <v>61</v>
+        <v>58.63</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="DM5" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DN5" t="n">
-        <v>10.8</v>
+        <v>10.64</v>
       </c>
       <c r="DO5" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="DP5" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DS5" t="n">
         <v>0</v>
       </c>
       <c r="DT5" t="n">
-        <v>57.5</v>
+        <v>57.27</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>13.1</v>
+        <v>12.73</v>
       </c>
       <c r="DW5" t="n">
-        <v>7.9</v>
+        <v>7.82</v>
       </c>
       <c r="DX5" t="n">
-        <v>5.2</v>
+        <v>4.91</v>
       </c>
       <c r="DY5" t="n">
-        <v>20.2</v>
+        <v>20.18</v>
       </c>
       <c r="DZ5" t="n">
-        <v>1.63</v>
+        <v>1.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="6">
@@ -2929,13 +2933,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0.25</v>
@@ -3019,139 +3023,139 @@
         <v>1.5</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>95.83</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>46.33</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.83</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>46.5</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ6" t="n">
         <v>0.8</v>
       </c>
-      <c r="AH6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>47.2</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10.6</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>45.8</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BC6" t="n">
+      <c r="BK6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="BP6" t="n">
         <v>4</v>
       </c>
-      <c r="BD6" t="n">
-        <v>16.6</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>7.67</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>4.22</v>
-      </c>
       <c r="BQ6" t="n">
-        <v>3.44</v>
+        <v>3.8</v>
       </c>
       <c r="BR6" t="n">
-        <v>88.89</v>
+        <v>90</v>
       </c>
       <c r="BS6" t="n">
-        <v>77.78</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
         <v>2.88</v>
@@ -3163,43 +3167,43 @@
         <v>3.68</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.91</v>
+        <v>3.92</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.21</v>
+        <v>4.33</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.65</v>
+        <v>4.75</v>
       </c>
       <c r="CE6" t="n">
         <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.68</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="CL6" t="n">
         <v>1.88</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="CO6" t="n">
         <v>1.22</v>
@@ -3208,7 +3212,7 @@
         <v>1.77</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3222,97 +3226,101 @@
       <c r="CU6" t="n">
         <v>1.49</v>
       </c>
-      <c r="CV6" t="inlineStr"/>
+      <c r="CV6" t="n">
+        <v>1.6</v>
+      </c>
       <c r="CW6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="CX6" t="inlineStr"/>
+        <v>1.78</v>
+      </c>
+      <c r="CX6" t="n">
+        <v>2.26</v>
+      </c>
       <c r="CY6" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="CZ6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DA6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DB6" t="n">
-        <v>2.92</v>
+        <v>2.95</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DD6" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DE6" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="DF6" t="n">
-        <v>95.22</v>
+        <v>95.7</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="DI6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DK6" t="n">
-        <v>54.89</v>
+        <v>53.6</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM6" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="DN6" t="n">
-        <v>12.89</v>
+        <v>12.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="DP6" t="n">
-        <v>8.44</v>
+        <v>7.9</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DS6" t="n">
         <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>46.56</v>
+        <v>46.9</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>11.22</v>
+        <v>11.6</v>
       </c>
       <c r="DW6" t="n">
-        <v>6.78</v>
+        <v>7.3</v>
       </c>
       <c r="DX6" t="n">
-        <v>4.44</v>
+        <v>4.3</v>
       </c>
       <c r="DY6" t="n">
-        <v>20</v>
+        <v>20.9</v>
       </c>
       <c r="DZ6" t="n">
         <v>1.42</v>
       </c>
       <c r="EA6" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="7">
@@ -3322,94 +3330,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F7" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="G7" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="H7" t="n">
-        <v>110.33</v>
+        <v>104.86</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.33</v>
+        <v>-0.29</v>
       </c>
       <c r="J7" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="K7" t="n">
-        <v>8.33</v>
+        <v>7.71</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="M7" t="n">
-        <v>66.33</v>
+        <v>60.14</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>5.17</v>
+        <v>4.71</v>
       </c>
       <c r="P7" t="n">
-        <v>11</v>
+        <v>11.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="R7" t="n">
-        <v>8</v>
+        <v>7.86</v>
       </c>
       <c r="S7" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="T7" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>58.5</v>
+        <v>56.57</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>17.17</v>
+        <v>15.57</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.33</v>
+        <v>10.29</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.83</v>
+        <v>5.29</v>
       </c>
       <c r="AC7" t="n">
-        <v>18.33</v>
+        <v>18</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.97</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.33</v>
+        <v>0.57</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -3493,70 +3501,70 @@
         <v>1.25</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.2</v>
+        <v>10.73</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="BP7" t="n">
-        <v>6.4</v>
+        <v>6.09</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="BR7" t="n">
-        <v>90</v>
+        <v>90.91</v>
       </c>
       <c r="BS7" t="n">
-        <v>80</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>40</v>
+        <v>36.36</v>
       </c>
       <c r="BU7" t="n">
-        <v>20</v>
+        <v>18.18</v>
       </c>
       <c r="BV7" t="n">
-        <v>10</v>
+        <v>9.09</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>60</v>
+        <v>63.64</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CB7" t="n">
-        <v>4.17</v>
+        <v>4.1</v>
       </c>
       <c r="CC7" t="n">
         <v>2.03</v>
@@ -3565,151 +3573,151 @@
         <v>2.28</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.17</v>
+        <v>3.11</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CK7" t="n">
         <v>1.43</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN7" t="n">
         <v>2</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.73</v>
+        <v>2.82</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="CV7" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CX7" t="n">
         <v>2.49</v>
       </c>
       <c r="CY7" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CZ7" t="n">
         <v>1.23</v>
       </c>
       <c r="DA7" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="DB7" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="DC7" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="DE7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="DF7" t="n">
-        <v>117.5</v>
+        <v>113.37</v>
       </c>
       <c r="DG7" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="DI7" t="n">
-        <v>7.7</v>
+        <v>7.36</v>
       </c>
       <c r="DJ7" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="DK7" t="n">
-        <v>68.2</v>
+        <v>64.09</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>4.6</v>
+        <v>4.36</v>
       </c>
       <c r="DN7" t="n">
-        <v>10.5</v>
+        <v>10.91</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="DP7" t="n">
-        <v>7.7</v>
+        <v>7.64</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>60.3</v>
+        <v>58.91</v>
       </c>
       <c r="DU7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DV7" t="n">
-        <v>15.4</v>
+        <v>14.54</v>
       </c>
       <c r="DW7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DX7" t="n">
-        <v>5.6</v>
+        <v>5.28</v>
       </c>
       <c r="DY7" t="n">
-        <v>20.6</v>
+        <v>20.18</v>
       </c>
       <c r="DZ7" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="8">
@@ -3719,94 +3727,94 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
       </c>
       <c r="E8" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H8" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>48</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P8" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="S8" t="n">
         <v>1</v>
       </c>
-      <c r="H8" t="n">
-        <v>99.5</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2</v>
-      </c>
-      <c r="K8" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="M8" t="n">
-        <v>47.25</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P8" t="n">
+      <c r="T8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>56</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>56.25</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>10.75</v>
-      </c>
       <c r="AA8" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.25</v>
+        <v>4.4</v>
       </c>
       <c r="AC8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AF8" t="n">
         <v>0.25</v>
@@ -3890,70 +3898,70 @@
         <v>3.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="BO8" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.38</v>
+        <v>3.78</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.38</v>
+        <v>2.89</v>
       </c>
       <c r="BR8" t="n">
         <v>100</v>
       </c>
       <c r="BS8" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT8" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
         <v>0</v>
       </c>
       <c r="BX8" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.68</v>
+        <v>2.63</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.87</v>
+        <v>3.82</v>
       </c>
       <c r="CC8" t="n">
         <v>3.94</v>
@@ -3965,25 +3973,25 @@
         <v>1.38</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="CG8" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="CI8" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CK8" t="n">
         <v>1.46</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CM8" t="n">
         <v>2.55</v>
@@ -3992,13 +4000,13 @@
         <v>1.97</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="CQ8" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CR8" t="n">
         <v>1.41</v>
@@ -4007,19 +4015,19 @@
         <v>3.04</v>
       </c>
       <c r="CT8" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CV8" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="CW8" t="n">
         <v>1.83</v>
       </c>
       <c r="CX8" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="CY8" t="n">
         <v>1.99</v>
@@ -4028,85 +4036,85 @@
         <v>1.3</v>
       </c>
       <c r="DA8" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DB8" t="n">
-        <v>3.36</v>
+        <v>3.38</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="DE8" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="DF8" t="n">
-        <v>87.25</v>
+        <v>89.56</v>
       </c>
       <c r="DG8" t="n">
         <v>0</v>
       </c>
       <c r="DH8" t="n">
-        <v>3.12</v>
+        <v>2.78</v>
       </c>
       <c r="DI8" t="n">
-        <v>4.88</v>
+        <v>4.44</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="DK8" t="n">
-        <v>42.88</v>
+        <v>43.78</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="DM8" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="DN8" t="n">
-        <v>12.75</v>
+        <v>12.11</v>
       </c>
       <c r="DO8" t="n">
-        <v>4.25</v>
+        <v>5.56</v>
       </c>
       <c r="DP8" t="n">
-        <v>6.88</v>
+        <v>6.78</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DR8" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>53.75</v>
+        <v>53.89</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DV8" t="n">
-        <v>10.88</v>
+        <v>11.56</v>
       </c>
       <c r="DW8" t="n">
-        <v>7.38</v>
+        <v>7.44</v>
       </c>
       <c r="DX8" t="n">
-        <v>3.5</v>
+        <v>4.11</v>
       </c>
       <c r="DY8" t="n">
-        <v>22.88</v>
+        <v>22.56</v>
       </c>
       <c r="DZ8" t="n">
-        <v>1.25</v>
+        <v>1.34</v>
       </c>
       <c r="EA8" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="9">
@@ -4116,13 +4124,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
         <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -4209,127 +4217,127 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AI9" t="n">
-        <v>91.25</v>
+        <v>88</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AL9" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>41.25</v>
+        <v>41.4</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AQ9" t="n">
-        <v>10.5</v>
+        <v>11.6</v>
       </c>
       <c r="AR9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="AS9" t="n">
-        <v>10.25</v>
+        <v>11.2</v>
       </c>
       <c r="AT9" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.5</v>
+        <v>45.8</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>3.75</v>
+        <v>6.2</v>
       </c>
       <c r="BB9" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="BC9" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="BD9" t="n">
-        <v>19</v>
+        <v>19.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.62</v>
+        <v>0.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="BG9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.5</v>
+        <v>10.22</v>
       </c>
       <c r="BI9" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN9" t="n">
         <v>1</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="BQ9" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU9" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV9" t="n">
         <v>0</v>
@@ -4338,7 +4346,7 @@
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY9" t="n">
         <v>4.01</v>
@@ -4347,55 +4355,55 @@
         <v>4.67</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.93</v>
+        <v>4.24</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.41</v>
+        <v>4.77</v>
       </c>
       <c r="CC9" t="n">
-        <v>5.58</v>
+        <v>6.66</v>
       </c>
       <c r="CD9" t="n">
-        <v>7.02</v>
+        <v>8.17</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="CI9" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.79</v>
+        <v>2.83</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="CR9" t="n">
         <v>1.36</v>
@@ -4413,97 +4421,97 @@
         <v>1.45</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="CX9" t="n">
         <v>2.59</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="CZ9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DA9" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DB9" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="DC9" t="n">
         <v>0</v>
       </c>
       <c r="DD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>84.22</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="DH9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="DI9" t="n">
+        <v>3</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="DL9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="DM9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DN9" t="n">
+        <v>11.89</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="DQ9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DR9" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>46.56</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="DW9" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="DX9" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="DY9" t="n">
+        <v>21.22</v>
+      </c>
+      <c r="DZ9" t="n">
         <v>0.88</v>
       </c>
-      <c r="DE9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="DF9" t="n">
-        <v>85.38</v>
-      </c>
-      <c r="DG9" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="DH9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="DI9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="DJ9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DK9" t="n">
-        <v>38</v>
-      </c>
-      <c r="DL9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="DM9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DN9" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="DO9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DP9" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="DQ9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DR9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DS9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT9" t="n">
-        <v>47.5</v>
-      </c>
-      <c r="DU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="DW9" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="DX9" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="DY9" t="n">
-        <v>21</v>
-      </c>
-      <c r="DZ9" t="n">
-        <v>0.8</v>
-      </c>
       <c r="EA9" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="10">
@@ -4513,94 +4521,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="F10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>83</v>
+        <v>87.5</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
-        <v>6.33</v>
+        <v>6.25</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="M10" t="n">
-        <v>44.67</v>
+        <v>43.75</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>3.67</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>12.33</v>
+        <v>10.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.67</v>
+        <v>4.75</v>
       </c>
       <c r="R10" t="n">
-        <v>9</v>
+        <v>9.25</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>44.33</v>
+        <v>45.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.33</v>
+        <v>0.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AA10" t="n">
-        <v>6.67</v>
+        <v>6</v>
       </c>
       <c r="AB10" t="n">
-        <v>3.33</v>
+        <v>4.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>28.33</v>
+        <v>27.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -4639,7 +4647,7 @@
         <v>10.67</v>
       </c>
       <c r="AR10" t="n">
-        <v>4.33</v>
+        <v>6.17</v>
       </c>
       <c r="AS10" t="n">
         <v>9.17</v>
@@ -4660,16 +4668,16 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>45.5</v>
+        <v>46.17</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>11.5</v>
+        <v>11.83</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.83</v>
       </c>
       <c r="BC10" t="n">
         <v>4</v>
@@ -4678,76 +4686,76 @@
         <v>21.33</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="BF10" t="n">
         <v>1.33</v>
       </c>
       <c r="BG10" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BH10" t="n">
         <v>9</v>
       </c>
       <c r="BI10" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.78</v>
+        <v>4.5</v>
       </c>
       <c r="BQ10" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>44.44</v>
+        <v>50</v>
       </c>
       <c r="BT10" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BU10" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BV10" t="n">
-        <v>22.22</v>
+        <v>20</v>
       </c>
       <c r="BW10" t="n">
-        <v>11.11</v>
+        <v>10</v>
       </c>
       <c r="BX10" t="n">
-        <v>33.33</v>
+        <v>40</v>
       </c>
       <c r="BY10" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="CA10" t="n">
         <v>3.63</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CC10" t="n">
         <v>2.92</v>
@@ -4759,31 +4767,31 @@
         <v>1.33</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="CL10" t="n">
         <v>1.83</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="CO10" t="n">
         <v>1.21</v>
@@ -4792,7 +4800,7 @@
         <v>1.76</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
@@ -4807,100 +4815,100 @@
         <v>1.51</v>
       </c>
       <c r="CV10" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CX10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="CY10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="DC10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DD10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>2</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>81.8</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>40.4</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="DS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>46</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="DW10" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="DX10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="DY10" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="DZ10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="EA10" t="n">
         <v>1.5</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="CX10" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="CY10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CZ10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="DA10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="DB10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="DC10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DD10" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="DE10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="DF10" t="n">
-        <v>79.67</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>40.34</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>11.22</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT10" t="n">
-        <v>45.11</v>
-      </c>
-      <c r="DU10" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DV10" t="n">
-        <v>11</v>
-      </c>
-      <c r="DW10" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="DX10" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="DY10" t="n">
-        <v>23.66</v>
-      </c>
-      <c r="DZ10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="EA10" t="n">
-        <v>1.55</v>
       </c>
     </row>
     <row r="11">
@@ -4910,13 +4918,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
         <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -4955,7 +4963,7 @@
         <v>12.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="R11" t="n">
         <v>5</v>
@@ -4976,7 +4984,7 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>58</v>
+        <v>57.2</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -5003,136 +5011,136 @@
         <v>0</v>
       </c>
       <c r="AG11" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>82.25</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>14.75</v>
+      </c>
+      <c r="AR11" t="n">
         <v>3</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AS11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF11" t="n">
         <v>3</v>
       </c>
-      <c r="AI11" t="n">
-        <v>81</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AL11" t="n">
+      <c r="BG11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BP11" t="n">
         <v>4.33</v>
       </c>
-      <c r="AM11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>52.33</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>46.33</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>19.67</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>10</v>
-      </c>
-      <c r="BI11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="BJ11" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BK11" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BN11" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BO11" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP11" t="n">
-        <v>4.12</v>
-      </c>
       <c r="BQ11" t="n">
-        <v>4.5</v>
+        <v>4.56</v>
       </c>
       <c r="BR11" t="n">
-        <v>87.5</v>
+        <v>88.89</v>
       </c>
       <c r="BS11" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BT11" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BU11" t="n">
-        <v>12.5</v>
+        <v>22.22</v>
       </c>
       <c r="BV11" t="n">
-        <v>0</v>
+        <v>11.11</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>37.5</v>
+        <v>44.44</v>
       </c>
       <c r="BY11" t="n">
         <v>2.3</v>
@@ -5141,46 +5149,46 @@
         <v>2.43</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="CC11" t="n">
-        <v>3.55</v>
+        <v>3.24</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.89</v>
+        <v>3.57</v>
       </c>
       <c r="CE11" t="n">
         <v>1.29</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI11" t="n">
         <v>2.26</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.81</v>
+        <v>2.84</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CO11" t="n">
         <v>1.18</v>
@@ -5189,7 +5197,7 @@
         <v>1.66</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5205,62 +5213,62 @@
       </c>
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="CZ11" t="n">
         <v>1.21</v>
       </c>
       <c r="DA11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DB11" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DC11" t="n">
         <v>0</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="DE11" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="DF11" t="n">
-        <v>103.38</v>
+        <v>101.44</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DI11" t="n">
-        <v>6</v>
+        <v>6.33</v>
       </c>
       <c r="DJ11" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DK11" t="n">
-        <v>62.62</v>
+        <v>61.67</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="DM11" t="n">
-        <v>1.87</v>
+        <v>2.22</v>
       </c>
       <c r="DN11" t="n">
-        <v>13.5</v>
+        <v>13.67</v>
       </c>
       <c r="DO11" t="n">
-        <v>3.13</v>
+        <v>3.67</v>
       </c>
       <c r="DP11" t="n">
-        <v>7.37</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
@@ -5272,28 +5280,28 @@
         <v>0</v>
       </c>
       <c r="DT11" t="n">
-        <v>53.62</v>
+        <v>54.56</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DV11" t="n">
-        <v>13.75</v>
+        <v>13.67</v>
       </c>
       <c r="DW11" t="n">
         <v>9</v>
       </c>
       <c r="DX11" t="n">
-        <v>4.75</v>
+        <v>4.67</v>
       </c>
       <c r="DY11" t="n">
-        <v>19.88</v>
+        <v>19.89</v>
       </c>
       <c r="DZ11" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="EA11" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="12">
@@ -5303,10 +5311,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" t="n">
         <v>4</v>
@@ -5315,49 +5323,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="H12" t="n">
-        <v>82.75</v>
+        <v>83.8</v>
       </c>
       <c r="I12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="K12" t="n">
-        <v>5.75</v>
+        <v>5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>47.25</v>
+        <v>46</v>
       </c>
       <c r="N12" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O12" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>13.5</v>
+        <v>13.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.75</v>
+        <v>4.2</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5369,28 +5377,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>45.25</v>
+        <v>43.6</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>10.25</v>
+        <v>8.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.75</v>
+        <v>4.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.25</v>
+        <v>20.8</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.31</v>
+        <v>1.14</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -5474,49 +5482,49 @@
         <v>2.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BH12" t="n">
-        <v>10</v>
+        <v>10.11</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="BO12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BP12" t="n">
-        <v>5.75</v>
+        <v>5.67</v>
       </c>
       <c r="BQ12" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>66.67</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.5</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV12" t="n">
         <v>0</v>
@@ -5525,19 +5533,19 @@
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>62.5</v>
+        <v>55.56</v>
       </c>
       <c r="BY12" t="n">
-        <v>3.49</v>
+        <v>3.36</v>
       </c>
       <c r="BZ12" t="n">
-        <v>3.47</v>
+        <v>3.46</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.64</v>
+        <v>3.6</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="CC12" t="n">
         <v>4.52</v>
@@ -5546,13 +5554,13 @@
         <v>4.86</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="CH12" t="n">
         <v>1.47</v>
@@ -5564,13 +5572,13 @@
         <v>1.65</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CN12" t="n">
         <v>2.1</v>
@@ -5579,22 +5587,22 @@
         <v>1.21</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.71</v>
+        <v>2.77</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV12" t="n">
         <v>1.5</v>
@@ -5612,52 +5620,52 @@
         <v>1.23</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="DB12" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="DC12" t="n">
         <v>0</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="DE12" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="DF12" t="n">
-        <v>90.25</v>
+        <v>90</v>
       </c>
       <c r="DG12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="DH12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="DI12" t="n">
-        <v>5</v>
+        <v>4.67</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DK12" t="n">
-        <v>52.62</v>
+        <v>51.33</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="DM12" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="DN12" t="n">
-        <v>12.25</v>
+        <v>12.56</v>
       </c>
       <c r="DO12" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="DP12" t="n">
-        <v>9.25</v>
+        <v>9.33</v>
       </c>
       <c r="DQ12" t="n">
         <v>0</v>
@@ -5669,28 +5677,28 @@
         <v>0</v>
       </c>
       <c r="DT12" t="n">
-        <v>46.62</v>
+        <v>45.56</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>10.62</v>
+        <v>9.56</v>
       </c>
       <c r="DW12" t="n">
-        <v>6.62</v>
+        <v>5.89</v>
       </c>
       <c r="DX12" t="n">
-        <v>4</v>
+        <v>3.67</v>
       </c>
       <c r="DY12" t="n">
-        <v>23.38</v>
+        <v>23.33</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="EA12" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="13">
@@ -5700,13 +5708,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E13" t="n">
         <v>0.5</v>
@@ -5748,7 +5756,7 @@
         <v>6</v>
       </c>
       <c r="R13" t="n">
-        <v>8.25</v>
+        <v>8</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -5766,7 +5774,7 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>44.25</v>
+        <v>43.75</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -5793,49 +5801,49 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="AI13" t="n">
-        <v>92.5</v>
+        <v>98.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>44.25</v>
+        <v>54</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="AR13" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="AS13" t="n">
-        <v>8.75</v>
+        <v>7.8</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AV13" t="n">
         <v>0</v>
@@ -5847,82 +5855,82 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>40.75</v>
+        <v>45.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.75</v>
+        <v>0.6</v>
       </c>
       <c r="BA13" t="n">
-        <v>9</v>
+        <v>11.6</v>
       </c>
       <c r="BB13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC13" t="n">
         <v>5</v>
       </c>
-      <c r="BC13" t="n">
-        <v>4</v>
-      </c>
       <c r="BD13" t="n">
-        <v>27.25</v>
+        <v>27.2</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.17</v>
+        <v>1.47</v>
       </c>
       <c r="BF13" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BG13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BH13" t="n">
-        <v>10.25</v>
+        <v>10.33</v>
       </c>
       <c r="BI13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="BN13" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.88</v>
+        <v>4.89</v>
       </c>
       <c r="BQ13" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="BR13" t="n">
-        <v>75</v>
+        <v>77.78</v>
       </c>
       <c r="BS13" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BT13" t="n">
-        <v>25</v>
+        <v>22.22</v>
       </c>
       <c r="BU13" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BV13" t="n">
-        <v>12.5</v>
+        <v>11.11</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="BY13" t="n">
         <v>2.74</v>
@@ -5931,31 +5939,31 @@
         <v>2.79</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="CC13" t="n">
-        <v>4.43</v>
+        <v>3.99</v>
       </c>
       <c r="CD13" t="n">
-        <v>4.53</v>
+        <v>4.06</v>
       </c>
       <c r="CE13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CG13" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.7</v>
@@ -5964,34 +5972,34 @@
         <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="CM13" t="n">
         <v>2.84</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO13" t="n">
         <v>1.24</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CQ13" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CV13" t="n">
         <v>1.48</v>
@@ -6009,85 +6017,85 @@
         <v>1.27</v>
       </c>
       <c r="DA13" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="DB13" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="DC13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DD13" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>2.88</v>
+        <v>3.11</v>
       </c>
       <c r="DF13" t="n">
-        <v>100</v>
+        <v>102.67</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="DH13" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="DI13" t="n">
-        <v>5.62</v>
+        <v>6</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DK13" t="n">
-        <v>46.88</v>
+        <v>52</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="DM13" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="DN13" t="n">
-        <v>14.75</v>
+        <v>14.78</v>
       </c>
       <c r="DO13" t="n">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="DP13" t="n">
-        <v>8.5</v>
+        <v>7.89</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="DS13" t="n">
         <v>0</v>
       </c>
       <c r="DT13" t="n">
-        <v>42.5</v>
+        <v>44.56</v>
       </c>
       <c r="DU13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="DV13" t="n">
-        <v>10.88</v>
+        <v>12.11</v>
       </c>
       <c r="DW13" t="n">
-        <v>6.62</v>
+        <v>7.33</v>
       </c>
       <c r="DX13" t="n">
-        <v>4.25</v>
+        <v>4.78</v>
       </c>
       <c r="DY13" t="n">
-        <v>25.75</v>
+        <v>25.89</v>
       </c>
       <c r="DZ13" t="n">
-        <v>1.32</v>
+        <v>1.47</v>
       </c>
       <c r="EA13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
+++ b/data/teams/leagues/Averages_Finland_Veikkausliiga_2026.xlsx
@@ -1635,16 +1635,16 @@
         <v>2.6</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="CV2" t="inlineStr"/>
       <c r="CW2" t="n">
@@ -2821,13 +2821,13 @@
         <v>1.38</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.12</v>
+        <v>3.16</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CV5" t="n">
         <v>1.54</v>
@@ -3059,7 +3059,7 @@
         <v>10.67</v>
       </c>
       <c r="AR6" t="n">
-        <v>2.17</v>
+        <v>1.5</v>
       </c>
       <c r="AS6" t="n">
         <v>7.83</v>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="AZ6" t="n">
         <v>0</v>
@@ -3284,7 +3284,7 @@
         <v>12.7</v>
       </c>
       <c r="DO6" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="DP6" t="n">
         <v>7.9</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="DT6" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
@@ -3612,16 +3612,16 @@
         <v>2.82</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.18</v>
+        <v>3.24</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="CV7" t="n">
         <v>1.49</v>
@@ -4566,7 +4566,7 @@
         <v>10.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="R10" t="n">
         <v>9.25</v>
@@ -4587,16 +4587,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>45.75</v>
+        <v>46.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0.25</v>
       </c>
       <c r="Z10" t="n">
-        <v>10.5</v>
+        <v>10.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="AB10" t="n">
         <v>4.5</v>
@@ -4605,7 +4605,7 @@
         <v>27.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
         <v>1.75</v>
@@ -4872,7 +4872,7 @@
         <v>10.5</v>
       </c>
       <c r="DO10" t="n">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="DP10" t="n">
         <v>9.199999999999999</v>
@@ -4887,16 +4887,16 @@
         <v>0</v>
       </c>
       <c r="DT10" t="n">
-        <v>46</v>
+        <v>46.3</v>
       </c>
       <c r="DU10" t="n">
         <v>0.1</v>
       </c>
       <c r="DV10" t="n">
-        <v>11.3</v>
+        <v>11.2</v>
       </c>
       <c r="DW10" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="DX10" t="n">
         <v>4.2</v>
@@ -4905,7 +4905,7 @@
         <v>23.9</v>
       </c>
       <c r="DZ10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="EA10" t="n">
         <v>1.5</v>
@@ -5203,21 +5203,21 @@
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CT11" t="n">
         <v>3.3</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV11" t="inlineStr"/>
       <c r="CW11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CX11" t="inlineStr"/>
       <c r="CY11" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="CZ11" t="n">
         <v>1.21</v>
@@ -5608,13 +5608,13 @@
         <v>1.5</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="CX12" t="n">
         <v>2.46</v>
       </c>
       <c r="CY12" t="n">
-        <v>2.08</v>
+        <v>2.11</v>
       </c>
       <c r="CZ12" t="n">
         <v>1.23</v>
@@ -6011,7 +6011,7 @@
         <v>2.53</v>
       </c>
       <c r="CY13" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CZ13" t="n">
         <v>1.27</v>
